--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.11</v>
+        <v>225.8</v>
       </c>
       <c r="E2" t="n">
-        <v>11.55</v>
+        <v>187.35</v>
       </c>
       <c r="F2" t="n">
-        <v>22.11</v>
+        <v>20.52</v>
       </c>
       <c r="G2" t="n">
-        <v>12.8</v>
+        <v>216.6</v>
       </c>
       <c r="H2" t="n">
-        <v>10.23</v>
+        <v>4.25</v>
       </c>
       <c r="I2" t="n">
-        <v>64.90000000000001</v>
+        <v>61.49</v>
       </c>
       <c r="J2" t="n">
-        <v>2.12</v>
+        <v>4.15</v>
       </c>
       <c r="K2" t="n">
         <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>14.11</v>
+        <v>225.8</v>
       </c>
       <c r="O2" t="n">
-        <v>7087</v>
+        <v>442</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99997.57000000001</v>
+        <v>99803.60000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S2" t="n">
-        <v>12.7</v>
+        <v>203.22</v>
       </c>
       <c r="T2" t="n">
-        <v>9999.76</v>
+        <v>9980.360000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>17.07</v>
+        <v>273.22</v>
       </c>
       <c r="V2" t="n">
-        <v>20.98</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20979.49</v>
+        <v>20958.76</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>CALSOFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>575.5</v>
+        <v>24.6</v>
       </c>
       <c r="E3" t="n">
-        <v>514.6799999999999</v>
+        <v>17.32</v>
       </c>
       <c r="F3" t="n">
-        <v>11.82</v>
+        <v>42.01</v>
       </c>
       <c r="G3" t="n">
-        <v>570</v>
+        <v>21.42</v>
       </c>
       <c r="H3" t="n">
-        <v>0.96</v>
+        <v>14.85</v>
       </c>
       <c r="I3" t="n">
-        <v>69.12</v>
+        <v>65.59</v>
       </c>
       <c r="J3" t="n">
-        <v>17.84</v>
+        <v>1.98</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>77</v>
+        <v>83.5</v>
       </c>
       <c r="N3" t="n">
-        <v>575.5</v>
+        <v>24.6</v>
       </c>
       <c r="O3" t="n">
-        <v>173</v>
+        <v>4065</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99561.5</v>
+        <v>99999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>517.95</v>
+        <v>22.14</v>
       </c>
       <c r="T3" t="n">
-        <v>9956.15</v>
+        <v>9999.9</v>
       </c>
       <c r="U3" t="n">
-        <v>690.6</v>
+        <v>29.77</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>21.02</v>
       </c>
       <c r="W3" t="n">
-        <v>19912.3</v>
+        <v>21019.79</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>309.65</v>
+        <v>575.5</v>
       </c>
       <c r="E4" t="n">
-        <v>232.49</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>33.19</v>
+        <v>11.82</v>
       </c>
       <c r="G4" t="n">
-        <v>220.4</v>
+        <v>570</v>
       </c>
       <c r="H4" t="n">
-        <v>40.49</v>
+        <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>65.09999999999999</v>
+        <v>69.12</v>
       </c>
       <c r="J4" t="n">
-        <v>0.86</v>
+        <v>17.84</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
-        <v>309.65</v>
+        <v>575.5</v>
       </c>
       <c r="O4" t="n">
-        <v>322</v>
+        <v>173</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99707.3</v>
+        <v>99561.5</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>278.68</v>
+        <v>517.95</v>
       </c>
       <c r="T4" t="n">
-        <v>9970.73</v>
+        <v>9956.15</v>
       </c>
       <c r="U4" t="n">
-        <v>365.39</v>
+        <v>690.6</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W4" t="n">
-        <v>17947.31</v>
+        <v>19912.3</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -813,64 +813,64 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>182.04</v>
+        <v>309.65</v>
       </c>
       <c r="E5" t="n">
-        <v>181.4</v>
+        <v>231.56</v>
       </c>
       <c r="F5" t="n">
-        <v>0.35</v>
+        <v>33.72</v>
       </c>
       <c r="G5" t="n">
-        <v>150.79</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>20.72</v>
+        <v>40.49</v>
       </c>
       <c r="I5" t="n">
-        <v>42.67</v>
+        <v>65.56</v>
       </c>
       <c r="J5" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>75.8</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>182.04</v>
+        <v>309.65</v>
       </c>
       <c r="O5" t="n">
-        <v>549</v>
+        <v>322</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99939.96000000001</v>
+        <v>99707.3</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>163.84</v>
+        <v>278.68</v>
       </c>
       <c r="T5" t="n">
-        <v>9994</v>
+        <v>9970.73</v>
       </c>
       <c r="U5" t="n">
-        <v>214.81</v>
+        <v>365.39</v>
       </c>
       <c r="V5" t="n">
         <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17989.19</v>
+        <v>17947.31</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -898,64 +898,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.6</v>
+        <v>182.04</v>
       </c>
       <c r="E6" t="n">
-        <v>17.36</v>
+        <v>181.4</v>
       </c>
       <c r="F6" t="n">
-        <v>41.72</v>
+        <v>0.35</v>
       </c>
       <c r="G6" t="n">
-        <v>21.42</v>
+        <v>150.79</v>
       </c>
       <c r="H6" t="n">
-        <v>14.85</v>
+        <v>20.72</v>
       </c>
       <c r="I6" t="n">
-        <v>66.54000000000001</v>
+        <v>42.67</v>
       </c>
       <c r="J6" t="n">
-        <v>1.91</v>
+        <v>0.74</v>
       </c>
       <c r="K6" t="n">
-        <v>72.5</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
       <c r="N6" t="n">
-        <v>24.6</v>
+        <v>182.04</v>
       </c>
       <c r="O6" t="n">
-        <v>4065</v>
+        <v>549</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99999</v>
+        <v>99939.96000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>22.14</v>
+        <v>163.84</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.9</v>
+        <v>9994</v>
       </c>
       <c r="U6" t="n">
-        <v>29.77</v>
+        <v>214.81</v>
       </c>
       <c r="V6" t="n">
-        <v>21.02</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>21019.79</v>
+        <v>17989.19</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -986,10 +986,10 @@
         <v>351.3</v>
       </c>
       <c r="E7" t="n">
-        <v>289.05</v>
+        <v>287.84</v>
       </c>
       <c r="F7" t="n">
-        <v>21.54</v>
+        <v>22.05</v>
       </c>
       <c r="G7" t="n">
         <v>220</v>
@@ -998,10 +998,10 @@
         <v>59.68</v>
       </c>
       <c r="I7" t="n">
-        <v>52.36</v>
+        <v>53.46</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="K7" t="n">
         <v>57.5</v>
@@ -1241,10 +1241,10 @@
         <v>72.47</v>
       </c>
       <c r="E10" t="n">
-        <v>58.18</v>
+        <v>58.12</v>
       </c>
       <c r="F10" t="n">
-        <v>24.55</v>
+        <v>24.68</v>
       </c>
       <c r="G10" t="n">
         <v>68</v>
@@ -1253,10 +1253,10 @@
         <v>6.57</v>
       </c>
       <c r="I10" t="n">
-        <v>63.57</v>
+        <v>63.59</v>
       </c>
       <c r="J10" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>225.8</v>
+        <v>600.65</v>
       </c>
       <c r="E2" t="n">
-        <v>187.35</v>
+        <v>487.19</v>
       </c>
       <c r="F2" t="n">
-        <v>20.52</v>
+        <v>23.29</v>
       </c>
       <c r="G2" t="n">
-        <v>216.6</v>
+        <v>539</v>
       </c>
       <c r="H2" t="n">
-        <v>4.25</v>
+        <v>11.44</v>
       </c>
       <c r="I2" t="n">
-        <v>61.49</v>
+        <v>77.13</v>
       </c>
       <c r="J2" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>76.75</v>
       </c>
       <c r="N2" t="n">
-        <v>225.8</v>
+        <v>600.65</v>
       </c>
       <c r="O2" t="n">
-        <v>442</v>
+        <v>166</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99803.60000000001</v>
+        <v>99707.89999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>203.22</v>
+        <v>540.58</v>
       </c>
       <c r="T2" t="n">
-        <v>9980.360000000001</v>
+        <v>9970.790000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>273.22</v>
+        <v>696.75</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>20958.76</v>
+        <v>15953.26</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALSOFT</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.6</v>
+        <v>357</v>
       </c>
       <c r="E3" t="n">
-        <v>17.32</v>
+        <v>254.79</v>
       </c>
       <c r="F3" t="n">
-        <v>42.01</v>
+        <v>40.12</v>
       </c>
       <c r="G3" t="n">
-        <v>21.42</v>
+        <v>338.6</v>
       </c>
       <c r="H3" t="n">
-        <v>14.85</v>
+        <v>5.43</v>
       </c>
       <c r="I3" t="n">
-        <v>65.59</v>
+        <v>58.82</v>
       </c>
       <c r="J3" t="n">
-        <v>1.98</v>
+        <v>0.09</v>
       </c>
       <c r="K3" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>83.5</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>24.6</v>
+        <v>357</v>
       </c>
       <c r="O3" t="n">
-        <v>4065</v>
+        <v>280</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99999</v>
+        <v>99960</v>
       </c>
       <c r="R3" t="n">
         <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>22.14</v>
+        <v>321.3</v>
       </c>
       <c r="T3" t="n">
-        <v>9999.9</v>
+        <v>9996</v>
       </c>
       <c r="U3" t="n">
-        <v>29.77</v>
+        <v>421.26</v>
       </c>
       <c r="V3" t="n">
-        <v>21.02</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>21019.79</v>
+        <v>17992.8</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DICIND</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>575.5</v>
+        <v>1515</v>
       </c>
       <c r="E4" t="n">
-        <v>514.6799999999999</v>
+        <v>1259.44</v>
       </c>
       <c r="F4" t="n">
-        <v>11.82</v>
+        <v>20.29</v>
       </c>
       <c r="G4" t="n">
-        <v>570</v>
+        <v>1513</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96</v>
+        <v>0.13</v>
       </c>
       <c r="I4" t="n">
-        <v>69.12</v>
+        <v>73.63</v>
       </c>
       <c r="J4" t="n">
-        <v>17.84</v>
+        <v>3.17</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
         <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N4" t="n">
-        <v>575.5</v>
+        <v>1515</v>
       </c>
       <c r="O4" t="n">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99561.5</v>
+        <v>99990</v>
       </c>
       <c r="R4" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>517.95</v>
+        <v>1363.5</v>
       </c>
       <c r="T4" t="n">
-        <v>9956.15</v>
+        <v>9999</v>
       </c>
       <c r="U4" t="n">
-        <v>690.6</v>
+        <v>1787.7</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>19912.3</v>
+        <v>17998.2</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>309.65</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>231.56</v>
+        <v>58.28</v>
       </c>
       <c r="F5" t="n">
-        <v>33.72</v>
+        <v>23.9</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>68</v>
       </c>
       <c r="H5" t="n">
-        <v>40.49</v>
+        <v>6.19</v>
       </c>
       <c r="I5" t="n">
-        <v>65.56</v>
+        <v>62.51</v>
       </c>
       <c r="J5" t="n">
-        <v>0.88</v>
+        <v>0.36</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>73.55</v>
       </c>
       <c r="N5" t="n">
-        <v>309.65</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>322</v>
+        <v>1384</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99707.3</v>
+        <v>99938.64</v>
       </c>
       <c r="R5" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>278.68</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>9970.73</v>
+        <v>9993.860000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>365.39</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17947.31</v>
+        <v>17988.96</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>182.04</v>
+        <v>11789</v>
       </c>
       <c r="E6" t="n">
-        <v>181.4</v>
+        <v>8726.389999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.35</v>
+        <v>35.1</v>
       </c>
       <c r="G6" t="n">
-        <v>150.79</v>
+        <v>9950</v>
       </c>
       <c r="H6" t="n">
-        <v>20.72</v>
+        <v>18.48</v>
       </c>
       <c r="I6" t="n">
-        <v>42.67</v>
+        <v>58.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M6" t="n">
-        <v>75.8</v>
+        <v>71.55</v>
       </c>
       <c r="N6" t="n">
-        <v>182.04</v>
+        <v>11789</v>
       </c>
       <c r="O6" t="n">
-        <v>549</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99939.96000000001</v>
+        <v>94312</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.43</v>
       </c>
       <c r="S6" t="n">
-        <v>163.84</v>
+        <v>10610.1</v>
       </c>
       <c r="T6" t="n">
-        <v>9994</v>
+        <v>9431.200000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>214.81</v>
+        <v>13911.02</v>
       </c>
       <c r="V6" t="n">
         <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>17989.19</v>
+        <v>16976.16</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>351.3</v>
+        <v>1320.85</v>
       </c>
       <c r="E7" t="n">
-        <v>287.84</v>
+        <v>910.22</v>
       </c>
       <c r="F7" t="n">
-        <v>22.05</v>
+        <v>45.11</v>
       </c>
       <c r="G7" t="n">
-        <v>220</v>
+        <v>993.8</v>
       </c>
       <c r="H7" t="n">
-        <v>59.68</v>
+        <v>32.91</v>
       </c>
       <c r="I7" t="n">
-        <v>53.46</v>
+        <v>76.87</v>
       </c>
       <c r="J7" t="n">
-        <v>0.34</v>
+        <v>1.23</v>
       </c>
       <c r="K7" t="n">
-        <v>57.5</v>
+        <v>56.25</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>74.5</v>
+        <v>68.95</v>
       </c>
       <c r="N7" t="n">
-        <v>351.3</v>
+        <v>1320.85</v>
       </c>
       <c r="O7" t="n">
-        <v>284</v>
+        <v>75</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99769.2</v>
+        <v>99063.75</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.91</v>
       </c>
       <c r="S7" t="n">
-        <v>316.17</v>
+        <v>1188.76</v>
       </c>
       <c r="T7" t="n">
-        <v>9976.92</v>
+        <v>9906.379999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>404</v>
+        <v>1505.77</v>
       </c>
       <c r="V7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>14965.38</v>
+        <v>13868.92</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.08</v>
+        <v>487.1</v>
       </c>
       <c r="E8" t="n">
-        <v>14.77</v>
+        <v>326.76</v>
       </c>
       <c r="F8" t="n">
-        <v>42.69</v>
+        <v>49.07</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>342.2</v>
       </c>
       <c r="H8" t="n">
-        <v>21.15</v>
+        <v>42.34</v>
       </c>
       <c r="I8" t="n">
-        <v>68.7</v>
+        <v>54.77</v>
       </c>
       <c r="J8" t="n">
-        <v>0.29</v>
+        <v>0.89</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>21.08</v>
+        <v>487.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4743</v>
+        <v>205</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99982.44</v>
+        <v>99855.5</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>18.97</v>
+        <v>438.39</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.24</v>
+        <v>9985.549999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>24.87</v>
+        <v>550.42</v>
       </c>
       <c r="V8" t="n">
-        <v>17.98</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>17976.84</v>
+        <v>12981.22</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>550.4</v>
+        <v>11663</v>
       </c>
       <c r="E9" t="n">
-        <v>486.4</v>
+        <v>9798.559999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>13.16</v>
+        <v>19.03</v>
       </c>
       <c r="G9" t="n">
-        <v>539</v>
+        <v>10187</v>
       </c>
       <c r="H9" t="n">
-        <v>2.12</v>
+        <v>14.49</v>
       </c>
       <c r="I9" t="n">
-        <v>63.06</v>
+        <v>64.91</v>
       </c>
       <c r="J9" t="n">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="K9" t="n">
         <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>63.95</v>
       </c>
       <c r="N9" t="n">
-        <v>550.4</v>
+        <v>11663</v>
       </c>
       <c r="O9" t="n">
-        <v>181</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99622.39999999999</v>
+        <v>93304</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="S9" t="n">
-        <v>495.36</v>
+        <v>10496.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9962.24</v>
+        <v>9330.4</v>
       </c>
       <c r="U9" t="n">
-        <v>643.97</v>
+        <v>13412.45</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>16935.81</v>
+        <v>13995.6</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72.47</v>
+        <v>246.69</v>
       </c>
       <c r="E10" t="n">
-        <v>58.12</v>
+        <v>158.83</v>
       </c>
       <c r="F10" t="n">
-        <v>24.68</v>
+        <v>55.32</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>178.95</v>
       </c>
       <c r="H10" t="n">
-        <v>6.57</v>
+        <v>37.85</v>
       </c>
       <c r="I10" t="n">
-        <v>63.59</v>
+        <v>59.75</v>
       </c>
       <c r="J10" t="n">
-        <v>0.64</v>
+        <v>0.14</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>63.95</v>
       </c>
       <c r="N10" t="n">
-        <v>72.47</v>
+        <v>246.69</v>
       </c>
       <c r="O10" t="n">
-        <v>1379</v>
+        <v>405</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99936.13</v>
+        <v>99909.45</v>
       </c>
       <c r="R10" t="n">
         <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>65.22</v>
+        <v>222.02</v>
       </c>
       <c r="T10" t="n">
-        <v>9993.610000000001</v>
+        <v>9990.940000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>85.51000000000001</v>
+        <v>286.16</v>
       </c>
       <c r="V10" t="n">
-        <v>17.99</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>17978.51</v>
+        <v>15985.51</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>GOCLCORP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1081.9</v>
+        <v>408</v>
       </c>
       <c r="E11" t="n">
-        <v>983.5</v>
+        <v>324.52</v>
       </c>
       <c r="F11" t="n">
-        <v>10.01</v>
+        <v>25.72</v>
       </c>
       <c r="G11" t="n">
-        <v>1039.2</v>
+        <v>401.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.11</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="n">
-        <v>57.62</v>
+        <v>49.42</v>
       </c>
       <c r="J11" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>52.5</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>73.55</v>
+        <v>63.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1081.9</v>
+        <v>408</v>
       </c>
       <c r="O11" t="n">
-        <v>92</v>
+        <v>245</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99534.8</v>
+        <v>99960</v>
       </c>
       <c r="R11" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>973.71</v>
+        <v>367.2</v>
       </c>
       <c r="T11" t="n">
-        <v>9953.48</v>
+        <v>9996</v>
       </c>
       <c r="U11" t="n">
-        <v>1265.82</v>
+        <v>469.2</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>16920.92</v>
+        <v>14994</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,82 +549,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>600.65</v>
+        <v>3308</v>
       </c>
       <c r="E2" t="n">
-        <v>487.19</v>
+        <v>3235.82</v>
       </c>
       <c r="F2" t="n">
-        <v>23.29</v>
+        <v>2.23</v>
       </c>
       <c r="G2" t="n">
-        <v>539</v>
+        <v>3030</v>
       </c>
       <c r="H2" t="n">
-        <v>11.44</v>
+        <v>9.17</v>
       </c>
       <c r="I2" t="n">
-        <v>77.13</v>
+        <v>33.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>1.59</v>
       </c>
       <c r="K2" t="n">
-        <v>61.25</v>
+        <v>78.75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="M2" t="n">
-        <v>76.75</v>
+        <v>82.45</v>
       </c>
       <c r="N2" t="n">
-        <v>600.65</v>
+        <v>3308</v>
       </c>
       <c r="O2" t="n">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99707.89999999999</v>
+        <v>99240</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="S2" t="n">
-        <v>540.58</v>
+        <v>2977.2</v>
       </c>
       <c r="T2" t="n">
-        <v>9970.790000000001</v>
+        <v>9924</v>
       </c>
       <c r="U2" t="n">
-        <v>696.75</v>
+        <v>4068.84</v>
       </c>
       <c r="V2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="W2" t="n">
-        <v>15953.26</v>
+        <v>22825.2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>357</v>
+        <v>856.55</v>
       </c>
       <c r="E3" t="n">
-        <v>254.79</v>
+        <v>623.24</v>
       </c>
       <c r="F3" t="n">
-        <v>40.12</v>
+        <v>37.44</v>
       </c>
       <c r="G3" t="n">
-        <v>338.6</v>
+        <v>720</v>
       </c>
       <c r="H3" t="n">
-        <v>5.43</v>
+        <v>18.97</v>
       </c>
       <c r="I3" t="n">
-        <v>58.82</v>
+        <v>55.75</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09</v>
+        <v>2.01</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>357</v>
+        <v>856.55</v>
       </c>
       <c r="O3" t="n">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99960</v>
+        <v>99359.8</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="S3" t="n">
-        <v>321.3</v>
+        <v>770.9</v>
       </c>
       <c r="T3" t="n">
-        <v>9996</v>
+        <v>9935.98</v>
       </c>
       <c r="U3" t="n">
-        <v>421.26</v>
+        <v>1036.43</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>17992.8</v>
+        <v>20865.56</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1515</v>
+        <v>14.12</v>
       </c>
       <c r="E4" t="n">
-        <v>1259.44</v>
+        <v>11.6</v>
       </c>
       <c r="F4" t="n">
-        <v>20.29</v>
+        <v>21.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1513</v>
+        <v>12.8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.13</v>
+        <v>10.31</v>
       </c>
       <c r="I4" t="n">
-        <v>73.63</v>
+        <v>61.78</v>
       </c>
       <c r="J4" t="n">
-        <v>3.17</v>
+        <v>2.08</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
         <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N4" t="n">
-        <v>1515</v>
+        <v>14.12</v>
       </c>
       <c r="O4" t="n">
-        <v>66</v>
+        <v>7082</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99990</v>
+        <v>99997.84</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>1363.5</v>
+        <v>12.71</v>
       </c>
       <c r="T4" t="n">
-        <v>9999</v>
+        <v>9999.780000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>1787.7</v>
+        <v>17.09</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>21.03</v>
       </c>
       <c r="W4" t="n">
-        <v>17998.2</v>
+        <v>21029.55</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.20999999999999</v>
+        <v>310.75</v>
       </c>
       <c r="E5" t="n">
-        <v>58.28</v>
+        <v>232.82</v>
       </c>
       <c r="F5" t="n">
-        <v>23.9</v>
+        <v>33.47</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>6.19</v>
+        <v>40.99</v>
       </c>
       <c r="I5" t="n">
-        <v>62.51</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>73.55</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>72.20999999999999</v>
+        <v>310.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1384</v>
+        <v>321</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99938.64</v>
+        <v>99750.75</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>64.98999999999999</v>
+        <v>279.68</v>
       </c>
       <c r="T5" t="n">
-        <v>9993.860000000001</v>
+        <v>9975.08</v>
       </c>
       <c r="U5" t="n">
-        <v>85.20999999999999</v>
+        <v>366.69</v>
       </c>
       <c r="V5" t="n">
         <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17988.96</v>
+        <v>17955.13</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11789</v>
+        <v>357.8</v>
       </c>
       <c r="E6" t="n">
-        <v>8726.389999999999</v>
+        <v>289.05</v>
       </c>
       <c r="F6" t="n">
-        <v>35.1</v>
+        <v>23.78</v>
       </c>
       <c r="G6" t="n">
-        <v>9950</v>
+        <v>220</v>
       </c>
       <c r="H6" t="n">
-        <v>18.48</v>
+        <v>62.64</v>
       </c>
       <c r="I6" t="n">
-        <v>58.6</v>
+        <v>58.96</v>
       </c>
       <c r="J6" t="n">
-        <v>0.31</v>
+        <v>0.59</v>
       </c>
       <c r="K6" t="n">
         <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>71.55</v>
+        <v>76.75</v>
       </c>
       <c r="N6" t="n">
-        <v>11789</v>
+        <v>357.8</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>94312</v>
+        <v>99826.2</v>
       </c>
       <c r="R6" t="n">
-        <v>9.43</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>10610.1</v>
+        <v>322.02</v>
       </c>
       <c r="T6" t="n">
-        <v>9431.200000000001</v>
+        <v>9982.620000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>13911.02</v>
+        <v>422.2</v>
       </c>
       <c r="V6" t="n">
         <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>16976.16</v>
+        <v>17968.72</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1320.85</v>
+        <v>575</v>
       </c>
       <c r="E7" t="n">
-        <v>910.22</v>
+        <v>440.75</v>
       </c>
       <c r="F7" t="n">
-        <v>45.11</v>
+        <v>30.46</v>
       </c>
       <c r="G7" t="n">
-        <v>993.8</v>
+        <v>552.5</v>
       </c>
       <c r="H7" t="n">
-        <v>32.91</v>
+        <v>4.07</v>
       </c>
       <c r="I7" t="n">
-        <v>76.87</v>
+        <v>59.39</v>
       </c>
       <c r="J7" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>56.25</v>
+        <v>66.25</v>
       </c>
       <c r="L7" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M7" t="n">
-        <v>68.95</v>
+        <v>76.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1320.85</v>
+        <v>575</v>
       </c>
       <c r="O7" t="n">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99063.75</v>
+        <v>99475</v>
       </c>
       <c r="R7" t="n">
-        <v>9.91</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>1188.76</v>
+        <v>517.5</v>
       </c>
       <c r="T7" t="n">
-        <v>9906.379999999999</v>
+        <v>9947.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1505.77</v>
+        <v>678.5</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>13868.92</v>
+        <v>17905.5</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,82 +1059,82 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>487.1</v>
+        <v>183.08</v>
       </c>
       <c r="E8" t="n">
-        <v>326.76</v>
+        <v>181.63</v>
       </c>
       <c r="F8" t="n">
-        <v>49.07</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>342.2</v>
+        <v>150.79</v>
       </c>
       <c r="H8" t="n">
-        <v>42.34</v>
+        <v>21.41</v>
       </c>
       <c r="I8" t="n">
-        <v>54.77</v>
+        <v>44.27</v>
       </c>
       <c r="J8" t="n">
-        <v>0.89</v>
+        <v>0.43</v>
       </c>
       <c r="K8" t="n">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>64.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="N8" t="n">
-        <v>487.1</v>
+        <v>183.08</v>
       </c>
       <c r="O8" t="n">
-        <v>205</v>
+        <v>546</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99855.5</v>
+        <v>99961.67999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>438.39</v>
+        <v>164.77</v>
       </c>
       <c r="T8" t="n">
-        <v>9985.549999999999</v>
+        <v>9996.17</v>
       </c>
       <c r="U8" t="n">
-        <v>550.42</v>
+        <v>216.03</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>12981.22</v>
+        <v>17993.1</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11663</v>
+        <v>701.55</v>
       </c>
       <c r="E9" t="n">
-        <v>9798.559999999999</v>
+        <v>506.88</v>
       </c>
       <c r="F9" t="n">
-        <v>19.03</v>
+        <v>38.41</v>
       </c>
       <c r="G9" t="n">
-        <v>10187</v>
+        <v>582.45</v>
       </c>
       <c r="H9" t="n">
-        <v>14.49</v>
+        <v>20.45</v>
       </c>
       <c r="I9" t="n">
-        <v>64.91</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.45</v>
+        <v>4.17</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>63.95</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>11663</v>
+        <v>701.55</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>93304</v>
+        <v>99620.10000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>9.33</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>10496.7</v>
+        <v>631.4</v>
       </c>
       <c r="T9" t="n">
-        <v>9330.4</v>
+        <v>9962.01</v>
       </c>
       <c r="U9" t="n">
-        <v>13412.45</v>
+        <v>834.84</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>13995.6</v>
+        <v>18927.82</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>246.69</v>
+        <v>609.75</v>
       </c>
       <c r="E10" t="n">
-        <v>158.83</v>
+        <v>487.41</v>
       </c>
       <c r="F10" t="n">
-        <v>55.32</v>
+        <v>25.1</v>
       </c>
       <c r="G10" t="n">
-        <v>178.95</v>
+        <v>539</v>
       </c>
       <c r="H10" t="n">
-        <v>37.85</v>
+        <v>13.13</v>
       </c>
       <c r="I10" t="n">
-        <v>59.75</v>
+        <v>77.94</v>
       </c>
       <c r="J10" t="n">
-        <v>0.14</v>
+        <v>2.53</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="M10" t="n">
-        <v>63.95</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>246.69</v>
+        <v>609.75</v>
       </c>
       <c r="O10" t="n">
-        <v>405</v>
+        <v>164</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99909.45</v>
+        <v>99999</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>222.02</v>
+        <v>548.78</v>
       </c>
       <c r="T10" t="n">
-        <v>9990.940000000001</v>
+        <v>9999.9</v>
       </c>
       <c r="U10" t="n">
-        <v>286.16</v>
+        <v>707.3099999999999</v>
       </c>
       <c r="V10" t="n">
         <v>16</v>
       </c>
       <c r="W10" t="n">
-        <v>15985.51</v>
+        <v>15999.84</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>408</v>
+        <v>20.37</v>
       </c>
       <c r="E11" t="n">
-        <v>324.52</v>
+        <v>14.83</v>
       </c>
       <c r="F11" t="n">
-        <v>25.72</v>
+        <v>37.33</v>
       </c>
       <c r="G11" t="n">
-        <v>401.7</v>
+        <v>17.4</v>
       </c>
       <c r="H11" t="n">
-        <v>1.57</v>
+        <v>17.07</v>
       </c>
       <c r="I11" t="n">
-        <v>49.42</v>
+        <v>60.63</v>
       </c>
       <c r="J11" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="K11" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>63.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>408</v>
+        <v>20.37</v>
       </c>
       <c r="O11" t="n">
-        <v>245</v>
+        <v>4909</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99960</v>
+        <v>99996.33</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>367.2</v>
+        <v>18.33</v>
       </c>
       <c r="T11" t="n">
-        <v>9996</v>
+        <v>9999.629999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>469.2</v>
+        <v>24.04</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>18.02</v>
       </c>
       <c r="W11" t="n">
-        <v>14994</v>
+        <v>18019.34</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3308</v>
+        <v>324.05</v>
       </c>
       <c r="E2" t="n">
-        <v>3235.82</v>
+        <v>233.52</v>
       </c>
       <c r="F2" t="n">
-        <v>2.23</v>
+        <v>38.77</v>
       </c>
       <c r="G2" t="n">
-        <v>3030</v>
+        <v>220.4</v>
       </c>
       <c r="H2" t="n">
-        <v>9.17</v>
+        <v>47.03</v>
       </c>
       <c r="I2" t="n">
-        <v>33.04</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>78.75</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>82.45</v>
+        <v>82</v>
       </c>
       <c r="N2" t="n">
-        <v>3308</v>
+        <v>324.05</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>308</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99240</v>
+        <v>99807.39999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="S2" t="n">
-        <v>2977.2</v>
+        <v>291.65</v>
       </c>
       <c r="T2" t="n">
-        <v>9924</v>
+        <v>9980.74</v>
       </c>
       <c r="U2" t="n">
-        <v>4068.84</v>
+        <v>382.38</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>22825.2</v>
+        <v>17965.33</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>STRONG RETEST</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>856.55</v>
+        <v>370.85</v>
       </c>
       <c r="E3" t="n">
-        <v>623.24</v>
+        <v>321.31</v>
       </c>
       <c r="F3" t="n">
-        <v>37.44</v>
+        <v>15.42</v>
       </c>
       <c r="G3" t="n">
-        <v>720</v>
+        <v>386</v>
       </c>
       <c r="H3" t="n">
-        <v>18.97</v>
+        <v>-3.92</v>
       </c>
       <c r="I3" t="n">
-        <v>55.75</v>
+        <v>58.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="L3" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>78.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="N3" t="n">
-        <v>856.55</v>
+        <v>370.85</v>
       </c>
       <c r="O3" t="n">
-        <v>116</v>
+        <v>269</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99359.8</v>
+        <v>99758.64999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.94</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>770.9</v>
+        <v>333.77</v>
       </c>
       <c r="T3" t="n">
-        <v>9935.98</v>
+        <v>9975.860000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>1036.43</v>
+        <v>437.6</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>20865.56</v>
+        <v>17956.56</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.12</v>
+        <v>358.8</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>289.67</v>
       </c>
       <c r="F4" t="n">
-        <v>21.72</v>
+        <v>23.87</v>
       </c>
       <c r="G4" t="n">
-        <v>12.8</v>
+        <v>220</v>
       </c>
       <c r="H4" t="n">
-        <v>10.31</v>
+        <v>63.09</v>
       </c>
       <c r="I4" t="n">
-        <v>61.78</v>
+        <v>59.77</v>
       </c>
       <c r="J4" t="n">
-        <v>2.08</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>14.12</v>
+        <v>358.8</v>
       </c>
       <c r="O4" t="n">
-        <v>7082</v>
+        <v>278</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99997.84</v>
+        <v>99746.39999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>12.71</v>
+        <v>322.92</v>
       </c>
       <c r="T4" t="n">
-        <v>9999.780000000001</v>
+        <v>9974.639999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>17.09</v>
+        <v>423.38</v>
       </c>
       <c r="V4" t="n">
-        <v>21.03</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>21029.55</v>
+        <v>17954.35</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>310.75</v>
+        <v>181.81</v>
       </c>
       <c r="E5" t="n">
-        <v>232.82</v>
+        <v>181.74</v>
       </c>
       <c r="F5" t="n">
-        <v>33.47</v>
+        <v>0.04</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>150.79</v>
       </c>
       <c r="H5" t="n">
-        <v>40.99</v>
+        <v>20.57</v>
       </c>
       <c r="I5" t="n">
-        <v>64.81999999999999</v>
+        <v>42.85</v>
       </c>
       <c r="J5" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>65</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>75.8</v>
       </c>
       <c r="N5" t="n">
-        <v>310.75</v>
+        <v>181.81</v>
       </c>
       <c r="O5" t="n">
-        <v>321</v>
+        <v>550</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99750.75</v>
+        <v>99995.5</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>279.68</v>
+        <v>163.63</v>
       </c>
       <c r="T5" t="n">
-        <v>9975.08</v>
+        <v>9999.549999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>366.69</v>
+        <v>214.54</v>
       </c>
       <c r="V5" t="n">
         <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>17955.13</v>
+        <v>17999.19</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>RECOVERY WATCH</t>
         </is>
       </c>
     </row>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>357.8</v>
+        <v>703.75</v>
       </c>
       <c r="E6" t="n">
-        <v>289.05</v>
+        <v>507.65</v>
       </c>
       <c r="F6" t="n">
-        <v>23.78</v>
+        <v>38.63</v>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>582.45</v>
       </c>
       <c r="H6" t="n">
-        <v>62.64</v>
+        <v>20.83</v>
       </c>
       <c r="I6" t="n">
-        <v>58.96</v>
+        <v>68.73</v>
       </c>
       <c r="J6" t="n">
-        <v>0.59</v>
+        <v>2.41</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>76.75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>357.8</v>
+        <v>703.75</v>
       </c>
       <c r="O6" t="n">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99826.2</v>
+        <v>99932.5</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>322.02</v>
+        <v>633.38</v>
       </c>
       <c r="T6" t="n">
-        <v>9982.620000000001</v>
+        <v>9993.25</v>
       </c>
       <c r="U6" t="n">
-        <v>422.2</v>
+        <v>837.46</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>17968.72</v>
+        <v>18987.18</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>20.22</v>
       </c>
       <c r="E7" t="n">
-        <v>440.75</v>
+        <v>14.86</v>
       </c>
       <c r="F7" t="n">
-        <v>30.46</v>
+        <v>36.08</v>
       </c>
       <c r="G7" t="n">
-        <v>552.5</v>
+        <v>17.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.07</v>
+        <v>16.21</v>
       </c>
       <c r="I7" t="n">
-        <v>59.39</v>
+        <v>59.36</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>0.27</v>
       </c>
       <c r="K7" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>76.55</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>575</v>
+        <v>20.22</v>
       </c>
       <c r="O7" t="n">
-        <v>173</v>
+        <v>4945</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99475</v>
+        <v>99987.89999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>517.5</v>
+        <v>18.2</v>
       </c>
       <c r="T7" t="n">
-        <v>9947.5</v>
+        <v>9998.790000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>678.5</v>
+        <v>23.86</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17905.5</v>
+        <v>17997.82</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>183.08</v>
+        <v>71.8</v>
       </c>
       <c r="E8" t="n">
-        <v>181.63</v>
+        <v>58.41</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>22.92</v>
       </c>
       <c r="G8" t="n">
-        <v>150.79</v>
+        <v>68</v>
       </c>
       <c r="H8" t="n">
-        <v>21.41</v>
+        <v>5.59</v>
       </c>
       <c r="I8" t="n">
-        <v>44.27</v>
+        <v>60.54</v>
       </c>
       <c r="J8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
         <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>75.8</v>
+        <v>73.55</v>
       </c>
       <c r="N8" t="n">
-        <v>183.08</v>
+        <v>71.8</v>
       </c>
       <c r="O8" t="n">
-        <v>546</v>
+        <v>1392</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99961.67999999999</v>
+        <v>99945.60000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>164.77</v>
+        <v>64.62</v>
       </c>
       <c r="T8" t="n">
-        <v>9996.17</v>
+        <v>9994.559999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>216.03</v>
+        <v>84.72</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="W8" t="n">
-        <v>17993.1</v>
+        <v>17980.21</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>701.55</v>
+        <v>1075</v>
       </c>
       <c r="E9" t="n">
-        <v>506.88</v>
+        <v>986.41</v>
       </c>
       <c r="F9" t="n">
-        <v>38.41</v>
+        <v>8.98</v>
       </c>
       <c r="G9" t="n">
-        <v>582.45</v>
+        <v>1039.2</v>
       </c>
       <c r="H9" t="n">
-        <v>20.45</v>
+        <v>3.44</v>
       </c>
       <c r="I9" t="n">
-        <v>68.43000000000001</v>
+        <v>55.34</v>
       </c>
       <c r="J9" t="n">
-        <v>4.17</v>
+        <v>0.62</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="M9" t="n">
-        <v>74.59999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N9" t="n">
-        <v>701.55</v>
+        <v>1075</v>
       </c>
       <c r="O9" t="n">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99620.10000000001</v>
+        <v>99975</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>631.4</v>
+        <v>967.5</v>
       </c>
       <c r="T9" t="n">
-        <v>9962.01</v>
+        <v>9997.5</v>
       </c>
       <c r="U9" t="n">
-        <v>834.84</v>
+        <v>1247</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>18927.82</v>
+        <v>15996</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>609.75</v>
+        <v>571.15</v>
       </c>
       <c r="E10" t="n">
-        <v>487.41</v>
+        <v>441.34</v>
       </c>
       <c r="F10" t="n">
-        <v>25.1</v>
+        <v>29.41</v>
       </c>
       <c r="G10" t="n">
-        <v>539</v>
+        <v>552.5</v>
       </c>
       <c r="H10" t="n">
-        <v>13.13</v>
+        <v>3.38</v>
       </c>
       <c r="I10" t="n">
-        <v>77.94</v>
+        <v>58.21</v>
       </c>
       <c r="J10" t="n">
-        <v>2.53</v>
+        <v>0.51</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>74.34999999999999</v>
+        <v>73.55</v>
       </c>
       <c r="N10" t="n">
-        <v>609.75</v>
+        <v>571.15</v>
       </c>
       <c r="O10" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99999</v>
+        <v>99951.25</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>548.78</v>
+        <v>514.04</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.9</v>
+        <v>9995.120000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>707.3099999999999</v>
+        <v>673.96</v>
       </c>
       <c r="V10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>15999.84</v>
+        <v>17991.22</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20.37</v>
+        <v>714.15</v>
       </c>
       <c r="E11" t="n">
-        <v>14.83</v>
+        <v>539.58</v>
       </c>
       <c r="F11" t="n">
-        <v>37.33</v>
+        <v>32.35</v>
       </c>
       <c r="G11" t="n">
-        <v>17.4</v>
+        <v>659.2</v>
       </c>
       <c r="H11" t="n">
-        <v>17.07</v>
+        <v>8.34</v>
       </c>
       <c r="I11" t="n">
-        <v>60.63</v>
+        <v>47.25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42</v>
+        <v>1.86</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>63.75</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M11" t="n">
-        <v>74.34999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="N11" t="n">
-        <v>20.37</v>
+        <v>714.15</v>
       </c>
       <c r="O11" t="n">
-        <v>4909</v>
+        <v>140</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99996.33</v>
+        <v>99981</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>18.33</v>
+        <v>642.74</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.629999999999</v>
+        <v>9998.1</v>
       </c>
       <c r="U11" t="n">
-        <v>24.04</v>
+        <v>842.7</v>
       </c>
       <c r="V11" t="n">
-        <v>18.02</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>18019.34</v>
+        <v>17996.58</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>GOCLCORP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>324.05</v>
+        <v>398.25</v>
       </c>
       <c r="E2" t="n">
-        <v>233.52</v>
+        <v>324.85</v>
       </c>
       <c r="F2" t="n">
-        <v>38.77</v>
+        <v>22.59</v>
       </c>
       <c r="G2" t="n">
-        <v>220.4</v>
+        <v>401.7</v>
       </c>
       <c r="H2" t="n">
-        <v>47.03</v>
+        <v>-0.86</v>
       </c>
       <c r="I2" t="n">
-        <v>71.45999999999999</v>
+        <v>45.37</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0.21</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>51.25</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M2" t="n">
-        <v>82</v>
+        <v>62.75</v>
       </c>
       <c r="N2" t="n">
-        <v>324.05</v>
+        <v>398.25</v>
       </c>
       <c r="O2" t="n">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99807.39999999999</v>
+        <v>99960.75</v>
       </c>
       <c r="R2" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>291.65</v>
+        <v>358.42</v>
       </c>
       <c r="T2" t="n">
-        <v>9980.74</v>
+        <v>9996.08</v>
       </c>
       <c r="U2" t="n">
-        <v>382.38</v>
+        <v>457.99</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>17965.33</v>
+        <v>14994.11</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>370.85</v>
+        <v>495.65</v>
       </c>
       <c r="E3" t="n">
-        <v>321.31</v>
+        <v>455.02</v>
       </c>
       <c r="F3" t="n">
-        <v>15.42</v>
+        <v>8.93</v>
       </c>
       <c r="G3" t="n">
-        <v>386</v>
+        <v>497.1</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.92</v>
+        <v>-0.29</v>
       </c>
       <c r="I3" t="n">
-        <v>58.4</v>
+        <v>46.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
-        <v>62.5</v>
+        <v>56.25</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M3" t="n">
-        <v>77.5</v>
+        <v>61.75</v>
       </c>
       <c r="N3" t="n">
-        <v>370.85</v>
+        <v>495.65</v>
       </c>
       <c r="O3" t="n">
-        <v>269</v>
+        <v>201</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99758.64999999999</v>
+        <v>99625.64999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>333.77</v>
+        <v>446.08</v>
       </c>
       <c r="T3" t="n">
-        <v>9975.860000000001</v>
+        <v>9962.559999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>437.6</v>
+        <v>550.17</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
-        <v>17956.56</v>
+        <v>10958.82</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SURYODAY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>358.8</v>
+        <v>154.54</v>
       </c>
       <c r="E4" t="n">
-        <v>289.67</v>
+        <v>149.4</v>
       </c>
       <c r="F4" t="n">
-        <v>23.87</v>
+        <v>3.44</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>161.48</v>
       </c>
       <c r="H4" t="n">
-        <v>63.09</v>
+        <v>-4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>59.77</v>
+        <v>37.73</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>60.8</v>
       </c>
       <c r="N4" t="n">
-        <v>358.8</v>
+        <v>154.54</v>
       </c>
       <c r="O4" t="n">
-        <v>278</v>
+        <v>647</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99746.39999999999</v>
+        <v>99987.38</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>322.92</v>
+        <v>139.09</v>
       </c>
       <c r="T4" t="n">
-        <v>9974.639999999999</v>
+        <v>9998.74</v>
       </c>
       <c r="U4" t="n">
-        <v>423.38</v>
+        <v>174.63</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>17954.35</v>
+        <v>12998.36</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>181.81</v>
+        <v>83.95</v>
       </c>
       <c r="E5" t="n">
-        <v>181.74</v>
+        <v>82.97</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>150.79</v>
+        <v>86.72</v>
       </c>
       <c r="H5" t="n">
-        <v>20.57</v>
+        <v>-3.19</v>
       </c>
       <c r="I5" t="n">
-        <v>42.85</v>
+        <v>45.42</v>
       </c>
       <c r="J5" t="n">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>75.8</v>
+        <v>59.9</v>
       </c>
       <c r="N5" t="n">
-        <v>181.81</v>
+        <v>83.95</v>
       </c>
       <c r="O5" t="n">
-        <v>550</v>
+        <v>1191</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99995.5</v>
+        <v>99984.45</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>163.63</v>
+        <v>75.56</v>
       </c>
       <c r="T5" t="n">
-        <v>9999.549999999999</v>
+        <v>9998.440000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>214.54</v>
+        <v>94.86</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>17999.19</v>
+        <v>12997.98</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>703.75</v>
+        <v>1698.9</v>
       </c>
       <c r="E6" t="n">
-        <v>507.65</v>
+        <v>1619.07</v>
       </c>
       <c r="F6" t="n">
-        <v>38.63</v>
+        <v>4.93</v>
       </c>
       <c r="G6" t="n">
-        <v>582.45</v>
+        <v>1788.3</v>
       </c>
       <c r="H6" t="n">
-        <v>20.83</v>
+        <v>-5</v>
       </c>
       <c r="I6" t="n">
-        <v>68.73</v>
+        <v>49.33</v>
       </c>
       <c r="J6" t="n">
-        <v>2.41</v>
+        <v>1.11</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>703.75</v>
+        <v>1698.9</v>
       </c>
       <c r="O6" t="n">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99932.5</v>
+        <v>98536.2</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.85</v>
       </c>
       <c r="S6" t="n">
-        <v>633.38</v>
+        <v>1529.01</v>
       </c>
       <c r="T6" t="n">
-        <v>9993.25</v>
+        <v>9853.620000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>837.46</v>
+        <v>1885.78</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>18987.18</v>
+        <v>10838.98</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>DHANBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.22</v>
+        <v>32.49</v>
       </c>
       <c r="E7" t="n">
-        <v>14.86</v>
+        <v>28.25</v>
       </c>
       <c r="F7" t="n">
-        <v>36.08</v>
+        <v>15.03</v>
       </c>
       <c r="G7" t="n">
-        <v>17.4</v>
+        <v>33.5</v>
       </c>
       <c r="H7" t="n">
-        <v>16.21</v>
+        <v>-3.01</v>
       </c>
       <c r="I7" t="n">
-        <v>59.36</v>
+        <v>46.39</v>
       </c>
       <c r="J7" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
-        <v>74.34999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="N7" t="n">
-        <v>20.22</v>
+        <v>32.49</v>
       </c>
       <c r="O7" t="n">
-        <v>4945</v>
+        <v>3077</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99987.89999999999</v>
+        <v>99971.73</v>
       </c>
       <c r="R7" t="n">
         <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>18.2</v>
+        <v>29.24</v>
       </c>
       <c r="T7" t="n">
-        <v>9998.790000000001</v>
+        <v>9997.17</v>
       </c>
       <c r="U7" t="n">
-        <v>23.86</v>
+        <v>36.39</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W7" t="n">
-        <v>17997.82</v>
+        <v>11996.61</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>71.8</v>
+        <v>2529.7</v>
       </c>
       <c r="E8" t="n">
-        <v>58.41</v>
+        <v>2004.75</v>
       </c>
       <c r="F8" t="n">
-        <v>22.92</v>
+        <v>26.18</v>
       </c>
       <c r="G8" t="n">
-        <v>68</v>
+        <v>2602</v>
       </c>
       <c r="H8" t="n">
-        <v>5.59</v>
+        <v>-2.78</v>
       </c>
       <c r="I8" t="n">
-        <v>60.54</v>
+        <v>49.38</v>
       </c>
       <c r="J8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>47.5</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="M8" t="n">
-        <v>73.55</v>
+        <v>56.5</v>
       </c>
       <c r="N8" t="n">
-        <v>71.8</v>
+        <v>2529.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1392</v>
+        <v>39</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99945.60000000001</v>
+        <v>98658.3</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>64.62</v>
+        <v>2276.73</v>
       </c>
       <c r="T8" t="n">
-        <v>9994.559999999999</v>
+        <v>9865.83</v>
       </c>
       <c r="U8" t="n">
-        <v>84.72</v>
+        <v>2858.56</v>
       </c>
       <c r="V8" t="n">
-        <v>17.99</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>17980.21</v>
+        <v>12825.58</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1075</v>
+        <v>45.16</v>
       </c>
       <c r="E9" t="n">
-        <v>986.41</v>
+        <v>41.42</v>
       </c>
       <c r="F9" t="n">
-        <v>8.98</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>1039.2</v>
+        <v>46.84</v>
       </c>
       <c r="H9" t="n">
-        <v>3.44</v>
+        <v>-3.59</v>
       </c>
       <c r="I9" t="n">
-        <v>55.34</v>
+        <v>43.56</v>
       </c>
       <c r="J9" t="n">
-        <v>0.62</v>
+        <v>1.17</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>45</v>
       </c>
       <c r="L9" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="M9" t="n">
-        <v>73.55</v>
+        <v>55.8</v>
       </c>
       <c r="N9" t="n">
-        <v>1075</v>
+        <v>45.16</v>
       </c>
       <c r="O9" t="n">
-        <v>93</v>
+        <v>2214</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99975</v>
+        <v>99984.24000000001</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>967.5</v>
+        <v>40.64</v>
       </c>
       <c r="T9" t="n">
-        <v>9997.5</v>
+        <v>9998.42</v>
       </c>
       <c r="U9" t="n">
-        <v>1247</v>
+        <v>50.13</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>11.01</v>
       </c>
       <c r="W9" t="n">
-        <v>15996</v>
+        <v>11008.26</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>AFIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>571.15</v>
+        <v>9.41</v>
       </c>
       <c r="E10" t="n">
-        <v>441.34</v>
+        <v>8.09</v>
       </c>
       <c r="F10" t="n">
-        <v>29.41</v>
+        <v>16.38</v>
       </c>
       <c r="G10" t="n">
-        <v>552.5</v>
+        <v>9.67</v>
       </c>
       <c r="H10" t="n">
-        <v>3.38</v>
+        <v>-2.69</v>
       </c>
       <c r="I10" t="n">
-        <v>58.21</v>
+        <v>46.88</v>
       </c>
       <c r="J10" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>47.5</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>73.55</v>
+        <v>55.7</v>
       </c>
       <c r="N10" t="n">
-        <v>571.15</v>
+        <v>9.41</v>
       </c>
       <c r="O10" t="n">
-        <v>175</v>
+        <v>10626</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99951.25</v>
+        <v>99990.66</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>514.04</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>9995.120000000001</v>
+        <v>9999.07</v>
       </c>
       <c r="U10" t="n">
-        <v>673.96</v>
+        <v>10.54</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>12.01</v>
       </c>
       <c r="W10" t="n">
-        <v>17991.22</v>
+        <v>12008.88</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>714.15</v>
+        <v>199.59</v>
       </c>
       <c r="E11" t="n">
-        <v>539.58</v>
+        <v>164.98</v>
       </c>
       <c r="F11" t="n">
-        <v>32.35</v>
+        <v>20.98</v>
       </c>
       <c r="G11" t="n">
-        <v>659.2</v>
+        <v>204.4</v>
       </c>
       <c r="H11" t="n">
-        <v>8.34</v>
+        <v>-2.35</v>
       </c>
       <c r="I11" t="n">
-        <v>47.25</v>
+        <v>39.39</v>
       </c>
       <c r="J11" t="n">
-        <v>1.86</v>
+        <v>0.92</v>
       </c>
       <c r="K11" t="n">
-        <v>63.75</v>
+        <v>42.5</v>
       </c>
       <c r="L11" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>73.45</v>
+        <v>55.5</v>
       </c>
       <c r="N11" t="n">
-        <v>714.15</v>
+        <v>199.59</v>
       </c>
       <c r="O11" t="n">
-        <v>140</v>
+        <v>501</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99981</v>
+        <v>99994.59</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>642.74</v>
+        <v>179.63</v>
       </c>
       <c r="T11" t="n">
-        <v>9998.1</v>
+        <v>9999.459999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>842.7</v>
+        <v>225.54</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>17996.58</v>
+        <v>12999.3</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>398.25</v>
+        <v>582.35</v>
       </c>
       <c r="E2" t="n">
-        <v>324.85</v>
+        <v>442.77</v>
       </c>
       <c r="F2" t="n">
-        <v>22.59</v>
+        <v>31.52</v>
       </c>
       <c r="G2" t="n">
-        <v>401.7</v>
+        <v>552.5</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.86</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>45.37</v>
+        <v>59.88</v>
       </c>
       <c r="J2" t="n">
-        <v>0.21</v>
+        <v>5.8</v>
       </c>
       <c r="K2" t="n">
-        <v>51.25</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M2" t="n">
-        <v>62.75</v>
+        <v>81.8</v>
       </c>
       <c r="N2" t="n">
-        <v>398.25</v>
+        <v>582.35</v>
       </c>
       <c r="O2" t="n">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99960.75</v>
+        <v>99581.85000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>358.42</v>
+        <v>524.12</v>
       </c>
       <c r="T2" t="n">
-        <v>9996.08</v>
+        <v>9958.18</v>
       </c>
       <c r="U2" t="n">
-        <v>457.99</v>
+        <v>704.64</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>14994.11</v>
+        <v>20912.19</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>495.65</v>
+        <v>511.85</v>
       </c>
       <c r="E3" t="n">
-        <v>455.02</v>
+        <v>301.74</v>
       </c>
       <c r="F3" t="n">
-        <v>8.93</v>
+        <v>69.63</v>
       </c>
       <c r="G3" t="n">
-        <v>497.1</v>
+        <v>298</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.29</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>46.2</v>
+        <v>69.41</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>56.25</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="M3" t="n">
-        <v>61.75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>495.65</v>
+        <v>511.85</v>
       </c>
       <c r="O3" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99625.64999999999</v>
+        <v>99810.75</v>
       </c>
       <c r="R3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>446.08</v>
+        <v>460.66</v>
       </c>
       <c r="T3" t="n">
-        <v>9962.559999999999</v>
+        <v>9981.08</v>
       </c>
       <c r="U3" t="n">
-        <v>550.17</v>
+        <v>619.34</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="W3" t="n">
-        <v>10958.82</v>
+        <v>20960.26</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SURYODAY</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154.54</v>
+        <v>203.59</v>
       </c>
       <c r="E4" t="n">
-        <v>149.4</v>
+        <v>182.41</v>
       </c>
       <c r="F4" t="n">
-        <v>3.44</v>
+        <v>11.61</v>
       </c>
       <c r="G4" t="n">
-        <v>161.48</v>
+        <v>205.9</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.3</v>
+        <v>-1.12</v>
       </c>
       <c r="I4" t="n">
-        <v>37.73</v>
+        <v>64.95</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08</v>
+        <v>4.88</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>72.5</v>
       </c>
       <c r="L4" t="n">
         <v>92</v>
       </c>
       <c r="M4" t="n">
-        <v>60.8</v>
+        <v>80.3</v>
       </c>
       <c r="N4" t="n">
-        <v>154.54</v>
+        <v>203.59</v>
       </c>
       <c r="O4" t="n">
-        <v>647</v>
+        <v>491</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99987.38</v>
+        <v>99962.69</v>
       </c>
       <c r="R4" t="n">
         <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>139.09</v>
+        <v>183.23</v>
       </c>
       <c r="T4" t="n">
-        <v>9998.74</v>
+        <v>9996.27</v>
       </c>
       <c r="U4" t="n">
-        <v>174.63</v>
+        <v>244.31</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="W4" t="n">
-        <v>12998.36</v>
+        <v>19992.54</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,82 +804,82 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>83.95</v>
+        <v>125.82</v>
       </c>
       <c r="E5" t="n">
-        <v>82.97</v>
+        <v>95.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>32.02</v>
       </c>
       <c r="G5" t="n">
-        <v>86.72</v>
+        <v>108.59</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.19</v>
+        <v>15.87</v>
       </c>
       <c r="I5" t="n">
-        <v>45.42</v>
+        <v>60.83</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>1.61</v>
       </c>
       <c r="K5" t="n">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>59.9</v>
+        <v>80.3</v>
       </c>
       <c r="N5" t="n">
-        <v>83.95</v>
+        <v>125.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1191</v>
+        <v>794</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99984.45</v>
+        <v>99901.08</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>75.56</v>
+        <v>113.24</v>
       </c>
       <c r="T5" t="n">
-        <v>9998.440000000001</v>
+        <v>9990.110000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>94.86</v>
+        <v>152.24</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="W5" t="n">
-        <v>12997.98</v>
+        <v>20979.23</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>RECOVERY WATCH</t>
+          <t>NOT A RECOVERY</t>
         </is>
       </c>
     </row>
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1698.9</v>
+        <v>361</v>
       </c>
       <c r="E6" t="n">
-        <v>1619.07</v>
+        <v>292.08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.93</v>
+        <v>23.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1788.3</v>
+        <v>220</v>
       </c>
       <c r="H6" t="n">
-        <v>-5</v>
+        <v>64.09</v>
       </c>
       <c r="I6" t="n">
-        <v>49.33</v>
+        <v>59.86</v>
       </c>
       <c r="J6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>66.25</v>
       </c>
       <c r="L6" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>79.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1698.9</v>
+        <v>361</v>
       </c>
       <c r="O6" t="n">
-        <v>58</v>
+        <v>277</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>98536.2</v>
+        <v>99997</v>
       </c>
       <c r="R6" t="n">
-        <v>9.85</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>1529.01</v>
+        <v>324.9</v>
       </c>
       <c r="T6" t="n">
-        <v>9853.620000000001</v>
+        <v>9999.700000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1885.78</v>
+        <v>425.98</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>10838.98</v>
+        <v>17999.46</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.49</v>
+        <v>1108.2</v>
       </c>
       <c r="E7" t="n">
-        <v>28.25</v>
+        <v>989.16</v>
       </c>
       <c r="F7" t="n">
-        <v>15.03</v>
+        <v>12.03</v>
       </c>
       <c r="G7" t="n">
-        <v>33.5</v>
+        <v>1039.2</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.01</v>
+        <v>6.64</v>
       </c>
       <c r="I7" t="n">
-        <v>46.39</v>
+        <v>63.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.26</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="M7" t="n">
-        <v>56.6</v>
+        <v>78.8</v>
       </c>
       <c r="N7" t="n">
-        <v>32.49</v>
+        <v>1108.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3077</v>
+        <v>90</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99971.73</v>
+        <v>99738</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>29.24</v>
+        <v>997.38</v>
       </c>
       <c r="T7" t="n">
-        <v>9997.17</v>
+        <v>9973.799999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>36.39</v>
+        <v>1307.68</v>
       </c>
       <c r="V7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>11996.61</v>
+        <v>17952.84</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2529.7</v>
+        <v>328.3</v>
       </c>
       <c r="E8" t="n">
-        <v>2004.75</v>
+        <v>236.01</v>
       </c>
       <c r="F8" t="n">
-        <v>26.18</v>
+        <v>39.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2602</v>
+        <v>220.4</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.78</v>
+        <v>48.96</v>
       </c>
       <c r="I8" t="n">
-        <v>49.38</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="K8" t="n">
-        <v>47.5</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>56.5</v>
+        <v>76.75</v>
       </c>
       <c r="N8" t="n">
-        <v>2529.7</v>
+        <v>328.3</v>
       </c>
       <c r="O8" t="n">
-        <v>39</v>
+        <v>304</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>98658.3</v>
+        <v>99803.2</v>
       </c>
       <c r="R8" t="n">
-        <v>9.869999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>2276.73</v>
+        <v>295.47</v>
       </c>
       <c r="T8" t="n">
-        <v>9865.83</v>
+        <v>9980.32</v>
       </c>
       <c r="U8" t="n">
-        <v>2858.56</v>
+        <v>387.39</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
-        <v>12825.58</v>
+        <v>17964.58</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>45.16</v>
+        <v>20.84</v>
       </c>
       <c r="E9" t="n">
-        <v>41.42</v>
+        <v>15.89</v>
       </c>
       <c r="F9" t="n">
-        <v>9.029999999999999</v>
+        <v>31.14</v>
       </c>
       <c r="G9" t="n">
-        <v>46.84</v>
+        <v>19.2</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.59</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>43.56</v>
+        <v>68.25</v>
       </c>
       <c r="J9" t="n">
-        <v>1.17</v>
+        <v>2.87</v>
       </c>
       <c r="K9" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>55.8</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>45.16</v>
+        <v>20.84</v>
       </c>
       <c r="O9" t="n">
-        <v>2214</v>
+        <v>4798</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99984.24000000001</v>
+        <v>99990.32000000001</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>40.64</v>
+        <v>18.76</v>
       </c>
       <c r="T9" t="n">
-        <v>9998.42</v>
+        <v>9999.030000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>50.13</v>
+        <v>24.8</v>
       </c>
       <c r="V9" t="n">
-        <v>11.01</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>11008.26</v>
+        <v>18998.16</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AFIL</t>
+          <t>AEROENTER</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.41</v>
+        <v>140.07</v>
       </c>
       <c r="E10" t="n">
-        <v>8.09</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>16.38</v>
+        <v>46.23</v>
       </c>
       <c r="G10" t="n">
-        <v>9.67</v>
+        <v>113.9</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.69</v>
+        <v>22.98</v>
       </c>
       <c r="I10" t="n">
-        <v>46.88</v>
+        <v>65.81</v>
       </c>
       <c r="J10" t="n">
-        <v>0.54</v>
+        <v>4.29</v>
       </c>
       <c r="K10" t="n">
-        <v>47.5</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M10" t="n">
-        <v>55.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>9.41</v>
+        <v>140.07</v>
       </c>
       <c r="O10" t="n">
-        <v>10626</v>
+        <v>713</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99990.66</v>
+        <v>99869.91</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>8.470000000000001</v>
+        <v>126.06</v>
       </c>
       <c r="T10" t="n">
-        <v>9999.07</v>
+        <v>9986.99</v>
       </c>
       <c r="U10" t="n">
-        <v>10.54</v>
+        <v>166.68</v>
       </c>
       <c r="V10" t="n">
-        <v>12.01</v>
+        <v>19</v>
       </c>
       <c r="W10" t="n">
-        <v>12008.88</v>
+        <v>18975.28</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>199.59</v>
+        <v>582.8</v>
       </c>
       <c r="E11" t="n">
-        <v>164.98</v>
+        <v>489.06</v>
       </c>
       <c r="F11" t="n">
-        <v>20.98</v>
+        <v>19.17</v>
       </c>
       <c r="G11" t="n">
-        <v>204.4</v>
+        <v>539</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.35</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>39.39</v>
+        <v>63.37</v>
       </c>
       <c r="J11" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="K11" t="n">
-        <v>42.5</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>55.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>199.59</v>
+        <v>582.8</v>
       </c>
       <c r="O11" t="n">
-        <v>501</v>
+        <v>171</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99994.59</v>
+        <v>99658.8</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>179.63</v>
+        <v>524.52</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.459999999999</v>
+        <v>9965.879999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>225.54</v>
+        <v>681.88</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>12999.3</v>
+        <v>16942</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -554,29 +554,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>582.35</v>
+        <v>581.55</v>
       </c>
       <c r="E2" t="n">
-        <v>442.77</v>
+        <v>443.35</v>
       </c>
       <c r="F2" t="n">
-        <v>31.52</v>
+        <v>31.17</v>
       </c>
       <c r="G2" t="n">
         <v>552.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>5.26</v>
       </c>
       <c r="I2" t="n">
-        <v>59.88</v>
+        <v>59.61</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
         <v>75</v>
@@ -588,7 +588,7 @@
         <v>81.8</v>
       </c>
       <c r="N2" t="n">
-        <v>582.35</v>
+        <v>581.55</v>
       </c>
       <c r="O2" t="n">
         <v>171</v>
@@ -597,25 +597,25 @@
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99581.85000000001</v>
+        <v>99445.05</v>
       </c>
       <c r="R2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="S2" t="n">
-        <v>524.12</v>
+        <v>523.4</v>
       </c>
       <c r="T2" t="n">
-        <v>9958.18</v>
+        <v>9944.5</v>
       </c>
       <c r="U2" t="n">
-        <v>704.64</v>
+        <v>703.6799999999999</v>
       </c>
       <c r="V2" t="n">
         <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20912.19</v>
+        <v>20883.46</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INDOBORAX</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>511.85</v>
+        <v>357.75</v>
       </c>
       <c r="E3" t="n">
-        <v>301.74</v>
+        <v>292.69</v>
       </c>
       <c r="F3" t="n">
-        <v>69.63</v>
+        <v>22.23</v>
       </c>
       <c r="G3" t="n">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
-        <v>71.76000000000001</v>
+        <v>62.61</v>
       </c>
       <c r="I3" t="n">
-        <v>69.41</v>
+        <v>56.02</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>1.12</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>80.59999999999999</v>
+        <v>79.75</v>
       </c>
       <c r="N3" t="n">
-        <v>511.85</v>
+        <v>357.75</v>
       </c>
       <c r="O3" t="n">
-        <v>195</v>
+        <v>279</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99810.75</v>
+        <v>99812.25</v>
       </c>
       <c r="R3" t="n">
         <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>460.66</v>
+        <v>321.98</v>
       </c>
       <c r="T3" t="n">
-        <v>9981.08</v>
+        <v>9981.219999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>619.34</v>
+        <v>422.14</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W3" t="n">
-        <v>20960.26</v>
+        <v>17966.21</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>203.59</v>
+        <v>249.71</v>
       </c>
       <c r="E4" t="n">
-        <v>182.41</v>
+        <v>208.06</v>
       </c>
       <c r="F4" t="n">
-        <v>11.61</v>
+        <v>20.02</v>
       </c>
       <c r="G4" t="n">
-        <v>205.9</v>
+        <v>241.57</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.12</v>
+        <v>3.37</v>
       </c>
       <c r="I4" t="n">
-        <v>64.95</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.88</v>
+        <v>1.74</v>
       </c>
       <c r="K4" t="n">
         <v>72.5</v>
       </c>
       <c r="L4" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>80.3</v>
+        <v>78.7</v>
       </c>
       <c r="N4" t="n">
-        <v>203.59</v>
+        <v>249.71</v>
       </c>
       <c r="O4" t="n">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99962.69</v>
+        <v>99884</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>183.23</v>
+        <v>224.74</v>
       </c>
       <c r="T4" t="n">
-        <v>9996.27</v>
+        <v>9988.4</v>
       </c>
       <c r="U4" t="n">
-        <v>244.31</v>
+        <v>302.15</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>19992.54</v>
+        <v>20975.64</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>125.82</v>
+        <v>1114</v>
       </c>
       <c r="E5" t="n">
-        <v>95.3</v>
+        <v>990.33</v>
       </c>
       <c r="F5" t="n">
-        <v>32.02</v>
+        <v>12.49</v>
       </c>
       <c r="G5" t="n">
-        <v>108.59</v>
+        <v>1039.2</v>
       </c>
       <c r="H5" t="n">
-        <v>15.87</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
-        <v>60.83</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>72.5</v>
+        <v>66.25</v>
       </c>
       <c r="L5" t="n">
         <v>92</v>
       </c>
       <c r="M5" t="n">
-        <v>80.3</v>
+        <v>76.55</v>
       </c>
       <c r="N5" t="n">
-        <v>125.82</v>
+        <v>1114</v>
       </c>
       <c r="O5" t="n">
-        <v>794</v>
+        <v>89</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99901.08</v>
+        <v>99146</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.91</v>
       </c>
       <c r="S5" t="n">
-        <v>113.24</v>
+        <v>1002.6</v>
       </c>
       <c r="T5" t="n">
-        <v>9990.110000000001</v>
+        <v>9914.6</v>
       </c>
       <c r="U5" t="n">
-        <v>152.24</v>
+        <v>1303.38</v>
       </c>
       <c r="V5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>20979.23</v>
+        <v>16854.82</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>361</v>
+        <v>199.74</v>
       </c>
       <c r="E6" t="n">
-        <v>292.08</v>
+        <v>182.6</v>
       </c>
       <c r="F6" t="n">
-        <v>23.6</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>205.9</v>
       </c>
       <c r="H6" t="n">
-        <v>64.09</v>
+        <v>-2.99</v>
       </c>
       <c r="I6" t="n">
-        <v>59.86</v>
+        <v>60.38</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>66.25</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>79.75</v>
+        <v>75.8</v>
       </c>
       <c r="N6" t="n">
-        <v>361</v>
+        <v>199.74</v>
       </c>
       <c r="O6" t="n">
-        <v>277</v>
+        <v>500</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99997</v>
+        <v>99870</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>324.9</v>
+        <v>179.77</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.700000000001</v>
+        <v>9987</v>
       </c>
       <c r="U6" t="n">
-        <v>425.98</v>
+        <v>233.7</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>17999.46</v>
+        <v>16977.9</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1108.2</v>
+        <v>234.32</v>
       </c>
       <c r="E7" t="n">
-        <v>989.16</v>
+        <v>194.9</v>
       </c>
       <c r="F7" t="n">
-        <v>12.03</v>
+        <v>20.22</v>
       </c>
       <c r="G7" t="n">
-        <v>1039.2</v>
+        <v>214</v>
       </c>
       <c r="H7" t="n">
-        <v>6.64</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>63.9</v>
+        <v>53.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>2.06</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>71.25</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M7" t="n">
-        <v>78.8</v>
+        <v>74.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1108.2</v>
+        <v>234.32</v>
       </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99738</v>
+        <v>99820.32000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>997.38</v>
+        <v>210.89</v>
       </c>
       <c r="T7" t="n">
-        <v>9973.799999999999</v>
+        <v>9982.030000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1307.68</v>
+        <v>276.5</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17952.84</v>
+        <v>17967.66</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>328.3</v>
+        <v>80.7</v>
       </c>
       <c r="E8" t="n">
-        <v>236.01</v>
+        <v>71.89</v>
       </c>
       <c r="F8" t="n">
-        <v>39.1</v>
+        <v>12.26</v>
       </c>
       <c r="G8" t="n">
-        <v>220.4</v>
+        <v>58.79</v>
       </c>
       <c r="H8" t="n">
-        <v>48.96</v>
+        <v>37.27</v>
       </c>
       <c r="I8" t="n">
-        <v>68.70999999999999</v>
+        <v>50.28</v>
       </c>
       <c r="J8" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L8" t="n">
         <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>76.75</v>
+        <v>74.5</v>
       </c>
       <c r="N8" t="n">
-        <v>328.3</v>
+        <v>80.7</v>
       </c>
       <c r="O8" t="n">
-        <v>304</v>
+        <v>1239</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99803.2</v>
+        <v>99987.3</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>295.47</v>
+        <v>72.63</v>
       </c>
       <c r="T8" t="n">
-        <v>9980.32</v>
+        <v>9998.73</v>
       </c>
       <c r="U8" t="n">
-        <v>387.39</v>
+        <v>92</v>
       </c>
       <c r="V8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>17964.58</v>
+        <v>13998.22</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIL</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.84</v>
+        <v>593</v>
       </c>
       <c r="E9" t="n">
-        <v>15.89</v>
+        <v>489.57</v>
       </c>
       <c r="F9" t="n">
-        <v>31.14</v>
+        <v>21.13</v>
       </c>
       <c r="G9" t="n">
-        <v>19.2</v>
+        <v>539</v>
       </c>
       <c r="H9" t="n">
-        <v>8.539999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I9" t="n">
-        <v>68.25</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>2.87</v>
+        <v>0.48</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>75</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>20.84</v>
+        <v>593</v>
       </c>
       <c r="O9" t="n">
-        <v>4798</v>
+        <v>168</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99990.32000000001</v>
+        <v>99624</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>18.76</v>
+        <v>533.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.030000000001</v>
+        <v>9962.4</v>
       </c>
       <c r="U9" t="n">
-        <v>24.8</v>
+        <v>699.74</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>18998.16</v>
+        <v>17932.32</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AEROENTER</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>140.07</v>
+        <v>20.09</v>
       </c>
       <c r="E10" t="n">
-        <v>95.79000000000001</v>
+        <v>14.97</v>
       </c>
       <c r="F10" t="n">
-        <v>46.23</v>
+        <v>34.16</v>
       </c>
       <c r="G10" t="n">
-        <v>113.9</v>
+        <v>17.4</v>
       </c>
       <c r="H10" t="n">
-        <v>22.98</v>
+        <v>15.46</v>
       </c>
       <c r="I10" t="n">
-        <v>65.81</v>
+        <v>57.39</v>
       </c>
       <c r="J10" t="n">
-        <v>4.29</v>
+        <v>0.06</v>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="M10" t="n">
-        <v>74.59999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>140.07</v>
+        <v>20.09</v>
       </c>
       <c r="O10" t="n">
-        <v>713</v>
+        <v>4977</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99869.91</v>
+        <v>99987.92999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>126.06</v>
+        <v>18.08</v>
       </c>
       <c r="T10" t="n">
-        <v>9986.99</v>
+        <v>9998.790000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>166.68</v>
+        <v>23.71</v>
       </c>
       <c r="V10" t="n">
-        <v>19</v>
+        <v>18.02</v>
       </c>
       <c r="W10" t="n">
-        <v>18975.28</v>
+        <v>18017.82</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>582.8</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>489.06</v>
+        <v>58.77</v>
       </c>
       <c r="F11" t="n">
-        <v>19.17</v>
+        <v>19.6</v>
       </c>
       <c r="G11" t="n">
-        <v>539</v>
+        <v>68</v>
       </c>
       <c r="H11" t="n">
-        <v>8.130000000000001</v>
+        <v>3.37</v>
       </c>
       <c r="I11" t="n">
-        <v>63.37</v>
+        <v>53.13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>62.5</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>74.34999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="N11" t="n">
-        <v>582.8</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>171</v>
+        <v>1422</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99658.8</v>
+        <v>99952.38</v>
       </c>
       <c r="R11" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>524.52</v>
+        <v>63.26</v>
       </c>
       <c r="T11" t="n">
-        <v>9965.879999999999</v>
+        <v>9995.24</v>
       </c>
       <c r="U11" t="n">
-        <v>681.88</v>
+        <v>80.13</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>16942</v>
+        <v>13993.33</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -554,68 +554,68 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>581.55</v>
+        <v>570.65</v>
       </c>
       <c r="E2" t="n">
-        <v>443.35</v>
+        <v>443.82</v>
       </c>
       <c r="F2" t="n">
-        <v>31.17</v>
+        <v>28.58</v>
       </c>
       <c r="G2" t="n">
         <v>552.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.26</v>
+        <v>3.29</v>
       </c>
       <c r="I2" t="n">
-        <v>59.61</v>
+        <v>55.92</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>1.58</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>81.8</v>
+        <v>83.5</v>
       </c>
       <c r="N2" t="n">
-        <v>581.55</v>
+        <v>570.65</v>
       </c>
       <c r="O2" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99445.05</v>
+        <v>99863.75</v>
       </c>
       <c r="R2" t="n">
-        <v>9.94</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>523.4</v>
+        <v>513.58</v>
       </c>
       <c r="T2" t="n">
-        <v>9944.5</v>
+        <v>9986.379999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>703.6799999999999</v>
+        <v>690.49</v>
       </c>
       <c r="V2" t="n">
         <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>20883.46</v>
+        <v>20971.39</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SPORTKING</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>357.75</v>
+        <v>228.26</v>
       </c>
       <c r="E3" t="n">
-        <v>292.69</v>
+        <v>137.76</v>
       </c>
       <c r="F3" t="n">
-        <v>22.23</v>
+        <v>65.7</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>140</v>
       </c>
       <c r="H3" t="n">
-        <v>62.61</v>
+        <v>63.04</v>
       </c>
       <c r="I3" t="n">
-        <v>56.02</v>
+        <v>64.66</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="K3" t="n">
-        <v>66.25</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>79.75</v>
+        <v>82</v>
       </c>
       <c r="N3" t="n">
-        <v>357.75</v>
+        <v>228.26</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>438</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99812.25</v>
+        <v>99977.88</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>321.98</v>
+        <v>205.43</v>
       </c>
       <c r="T3" t="n">
-        <v>9981.219999999999</v>
+        <v>9997.790000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>422.14</v>
+        <v>271.63</v>
       </c>
       <c r="V3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>17966.21</v>
+        <v>18995.8</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>249.71</v>
+        <v>129.62</v>
       </c>
       <c r="E4" t="n">
-        <v>208.06</v>
+        <v>95.61</v>
       </c>
       <c r="F4" t="n">
-        <v>20.02</v>
+        <v>35.57</v>
       </c>
       <c r="G4" t="n">
-        <v>241.57</v>
+        <v>108.59</v>
       </c>
       <c r="H4" t="n">
-        <v>3.37</v>
+        <v>19.37</v>
       </c>
       <c r="I4" t="n">
-        <v>64.40000000000001</v>
+        <v>64.72</v>
       </c>
       <c r="J4" t="n">
-        <v>1.74</v>
+        <v>2.82</v>
       </c>
       <c r="K4" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M4" t="n">
-        <v>78.7</v>
+        <v>81.8</v>
       </c>
       <c r="N4" t="n">
-        <v>249.71</v>
+        <v>129.62</v>
       </c>
       <c r="O4" t="n">
-        <v>400</v>
+        <v>771</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99884</v>
+        <v>99937.02</v>
       </c>
       <c r="R4" t="n">
         <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>224.74</v>
+        <v>116.66</v>
       </c>
       <c r="T4" t="n">
-        <v>9988.4</v>
+        <v>9993.700000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>302.15</v>
+        <v>156.84</v>
       </c>
       <c r="V4" t="n">
         <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>20975.64</v>
+        <v>20986.77</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1114</v>
+        <v>81.7</v>
       </c>
       <c r="E5" t="n">
-        <v>990.33</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>12.49</v>
+        <v>13.48</v>
       </c>
       <c r="G5" t="n">
-        <v>1039.2</v>
+        <v>58.79</v>
       </c>
       <c r="H5" t="n">
-        <v>7.2</v>
+        <v>38.97</v>
       </c>
       <c r="I5" t="n">
-        <v>65.15000000000001</v>
+        <v>54.34</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="K5" t="n">
-        <v>66.25</v>
+        <v>68.75</v>
       </c>
       <c r="L5" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>76.55</v>
+        <v>81.25</v>
       </c>
       <c r="N5" t="n">
-        <v>1114</v>
+        <v>81.7</v>
       </c>
       <c r="O5" t="n">
-        <v>89</v>
+        <v>1223</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99146</v>
+        <v>99919.10000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.91</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1002.6</v>
+        <v>73.53</v>
       </c>
       <c r="T5" t="n">
-        <v>9914.6</v>
+        <v>9991.91</v>
       </c>
       <c r="U5" t="n">
-        <v>1303.38</v>
+        <v>95.59</v>
       </c>
       <c r="V5" t="n">
         <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>16854.82</v>
+        <v>16986.25</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199.74</v>
+        <v>346.95</v>
       </c>
       <c r="E6" t="n">
-        <v>182.6</v>
+        <v>292.63</v>
       </c>
       <c r="F6" t="n">
-        <v>9.390000000000001</v>
+        <v>18.56</v>
       </c>
       <c r="G6" t="n">
-        <v>205.9</v>
+        <v>220</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.99</v>
+        <v>57.7</v>
       </c>
       <c r="I6" t="n">
-        <v>60.38</v>
+        <v>46.18</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>3.38</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>66.25</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>75.8</v>
+        <v>79.75</v>
       </c>
       <c r="N6" t="n">
-        <v>199.74</v>
+        <v>346.95</v>
       </c>
       <c r="O6" t="n">
-        <v>500</v>
+        <v>288</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99870</v>
+        <v>99921.60000000001</v>
       </c>
       <c r="R6" t="n">
         <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>179.77</v>
+        <v>312.26</v>
       </c>
       <c r="T6" t="n">
-        <v>9987</v>
+        <v>9992.16</v>
       </c>
       <c r="U6" t="n">
-        <v>233.7</v>
+        <v>405.93</v>
       </c>
       <c r="V6" t="n">
         <v>17</v>
       </c>
       <c r="W6" t="n">
-        <v>16977.9</v>
+        <v>16986.67</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>GEECEE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>234.32</v>
+        <v>368.65</v>
       </c>
       <c r="E7" t="n">
-        <v>194.9</v>
+        <v>321.82</v>
       </c>
       <c r="F7" t="n">
-        <v>20.22</v>
+        <v>14.55</v>
       </c>
       <c r="G7" t="n">
-        <v>214</v>
+        <v>386</v>
       </c>
       <c r="H7" t="n">
-        <v>9.5</v>
+        <v>-4.49</v>
       </c>
       <c r="I7" t="n">
-        <v>53.11</v>
+        <v>56.44</v>
       </c>
       <c r="J7" t="n">
-        <v>2.06</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>71.25</v>
+        <v>62.5</v>
       </c>
       <c r="L7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>74.75</v>
+        <v>77.5</v>
       </c>
       <c r="N7" t="n">
-        <v>234.32</v>
+        <v>368.65</v>
       </c>
       <c r="O7" t="n">
-        <v>426</v>
+        <v>271</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99820.32000000001</v>
+        <v>99904.14999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>210.89</v>
+        <v>331.78</v>
       </c>
       <c r="T7" t="n">
-        <v>9982.030000000001</v>
+        <v>9990.42</v>
       </c>
       <c r="U7" t="n">
-        <v>276.5</v>
+        <v>435.01</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17967.66</v>
+        <v>17982.75</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>80.7</v>
+        <v>666.25</v>
       </c>
       <c r="E8" t="n">
-        <v>71.89</v>
+        <v>532.25</v>
       </c>
       <c r="F8" t="n">
-        <v>12.26</v>
+        <v>25.18</v>
       </c>
       <c r="G8" t="n">
-        <v>58.79</v>
+        <v>675</v>
       </c>
       <c r="H8" t="n">
-        <v>37.27</v>
+        <v>-1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>50.28</v>
+        <v>66</v>
       </c>
       <c r="J8" t="n">
-        <v>0.83</v>
+        <v>3.23</v>
       </c>
       <c r="K8" t="n">
-        <v>57.5</v>
+        <v>72.5</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M8" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="N8" t="n">
-        <v>80.7</v>
+        <v>666.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1239</v>
+        <v>150</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99987.3</v>
+        <v>99937.5</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>72.63</v>
+        <v>599.62</v>
       </c>
       <c r="T8" t="n">
-        <v>9998.73</v>
+        <v>9993.75</v>
       </c>
       <c r="U8" t="n">
-        <v>92</v>
+        <v>806.16</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="W8" t="n">
-        <v>13998.22</v>
+        <v>20986.88</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>593</v>
+        <v>239.67</v>
       </c>
       <c r="E9" t="n">
-        <v>489.57</v>
+        <v>195.12</v>
       </c>
       <c r="F9" t="n">
-        <v>21.13</v>
+        <v>22.83</v>
       </c>
       <c r="G9" t="n">
-        <v>539</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
-        <v>10.02</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>66.23999999999999</v>
+        <v>57.44</v>
       </c>
       <c r="J9" t="n">
-        <v>0.48</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>593</v>
+        <v>239.67</v>
       </c>
       <c r="O9" t="n">
-        <v>168</v>
+        <v>417</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99624</v>
+        <v>99942.39</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>533.7</v>
+        <v>215.7</v>
       </c>
       <c r="T9" t="n">
-        <v>9962.4</v>
+        <v>9994.24</v>
       </c>
       <c r="U9" t="n">
-        <v>699.74</v>
+        <v>285.21</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W9" t="n">
-        <v>17932.32</v>
+        <v>18989.05</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,34 +1229,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.09</v>
+        <v>588</v>
       </c>
       <c r="E10" t="n">
-        <v>14.97</v>
+        <v>490.06</v>
       </c>
       <c r="F10" t="n">
-        <v>34.16</v>
+        <v>19.99</v>
       </c>
       <c r="G10" t="n">
-        <v>17.4</v>
+        <v>539</v>
       </c>
       <c r="H10" t="n">
-        <v>15.46</v>
+        <v>9.09</v>
       </c>
       <c r="I10" t="n">
-        <v>57.39</v>
+        <v>63.61</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06</v>
+        <v>0.95</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
@@ -1268,34 +1268,34 @@
         <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>20.09</v>
+        <v>588</v>
       </c>
       <c r="O10" t="n">
-        <v>4977</v>
+        <v>170</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99987.92999999999</v>
+        <v>99960</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>18.08</v>
+        <v>529.2</v>
       </c>
       <c r="T10" t="n">
-        <v>9998.790000000001</v>
+        <v>9996</v>
       </c>
       <c r="U10" t="n">
-        <v>23.71</v>
+        <v>687.96</v>
       </c>
       <c r="V10" t="n">
-        <v>18.02</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>18017.82</v>
+        <v>16993.2</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70.29000000000001</v>
+        <v>19.86</v>
       </c>
       <c r="E11" t="n">
-        <v>58.77</v>
+        <v>14.97</v>
       </c>
       <c r="F11" t="n">
-        <v>19.6</v>
+        <v>32.64</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>17.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.37</v>
+        <v>14.14</v>
       </c>
       <c r="I11" t="n">
-        <v>53.13</v>
+        <v>55.21</v>
       </c>
       <c r="J11" t="n">
-        <v>1.15</v>
+        <v>0.11</v>
       </c>
       <c r="K11" t="n">
-        <v>62.5</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>74.3</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>70.29000000000001</v>
+        <v>19.86</v>
       </c>
       <c r="O11" t="n">
-        <v>1422</v>
+        <v>5035</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99952.38</v>
+        <v>99995.10000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>63.26</v>
+        <v>17.87</v>
       </c>
       <c r="T11" t="n">
-        <v>9995.24</v>
+        <v>9999.51</v>
       </c>
       <c r="U11" t="n">
-        <v>80.13</v>
+        <v>23.43</v>
       </c>
       <c r="V11" t="n">
-        <v>14</v>
+        <v>17.98</v>
       </c>
       <c r="W11" t="n">
-        <v>13993.33</v>
+        <v>17979.12</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>570.65</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>443.82</v>
+        <v>72.13</v>
       </c>
       <c r="F2" t="n">
-        <v>28.58</v>
+        <v>18.67</v>
       </c>
       <c r="G2" t="n">
-        <v>552.5</v>
+        <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>3.29</v>
+        <v>45.6</v>
       </c>
       <c r="I2" t="n">
-        <v>55.92</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.58</v>
+        <v>4.38</v>
       </c>
       <c r="K2" t="n">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>83.5</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>570.65</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>175</v>
+        <v>1168</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99863.75</v>
+        <v>99980.8</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>513.58</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>9986.379999999999</v>
+        <v>9998.08</v>
       </c>
       <c r="U2" t="n">
-        <v>690.49</v>
+        <v>102.72</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>20971.39</v>
+        <v>19996.16</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SPORTKING</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>228.26</v>
+        <v>213.83</v>
       </c>
       <c r="E3" t="n">
-        <v>137.76</v>
+        <v>182.99</v>
       </c>
       <c r="F3" t="n">
-        <v>65.7</v>
+        <v>16.85</v>
       </c>
       <c r="G3" t="n">
-        <v>140</v>
+        <v>205.9</v>
       </c>
       <c r="H3" t="n">
-        <v>63.04</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>64.66</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4</v>
+        <v>4.29</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M3" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="N3" t="n">
-        <v>228.26</v>
+        <v>213.83</v>
       </c>
       <c r="O3" t="n">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99977.88</v>
+        <v>99858.61</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S3" t="n">
-        <v>205.43</v>
+        <v>192.45</v>
       </c>
       <c r="T3" t="n">
-        <v>9997.790000000001</v>
+        <v>9985.860000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>271.63</v>
+        <v>256.6</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>18995.8</v>
+        <v>19971.72</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>129.62</v>
+        <v>11800</v>
       </c>
       <c r="E4" t="n">
-        <v>95.61</v>
+        <v>8844.74</v>
       </c>
       <c r="F4" t="n">
-        <v>35.57</v>
+        <v>33.41</v>
       </c>
       <c r="G4" t="n">
-        <v>108.59</v>
+        <v>9950</v>
       </c>
       <c r="H4" t="n">
-        <v>19.37</v>
+        <v>18.59</v>
       </c>
       <c r="I4" t="n">
-        <v>64.72</v>
+        <v>56.56</v>
       </c>
       <c r="J4" t="n">
-        <v>2.82</v>
+        <v>1.46</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L4" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M4" t="n">
-        <v>81.8</v>
+        <v>76.8</v>
       </c>
       <c r="N4" t="n">
-        <v>129.62</v>
+        <v>11800</v>
       </c>
       <c r="O4" t="n">
-        <v>771</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99937.02</v>
+        <v>94400</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>9.44</v>
       </c>
       <c r="S4" t="n">
-        <v>116.66</v>
+        <v>10620</v>
       </c>
       <c r="T4" t="n">
-        <v>9993.700000000001</v>
+        <v>9440</v>
       </c>
       <c r="U4" t="n">
-        <v>156.84</v>
+        <v>14042</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W4" t="n">
-        <v>20986.77</v>
+        <v>17936</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81.7</v>
+        <v>293.5</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>267.93</v>
       </c>
       <c r="F5" t="n">
-        <v>13.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>58.79</v>
+        <v>290</v>
       </c>
       <c r="H5" t="n">
-        <v>38.97</v>
+        <v>1.21</v>
       </c>
       <c r="I5" t="n">
-        <v>54.34</v>
+        <v>53.34</v>
       </c>
       <c r="J5" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="K5" t="n">
-        <v>68.75</v>
+        <v>71.25</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M5" t="n">
-        <v>81.25</v>
+        <v>74.75</v>
       </c>
       <c r="N5" t="n">
-        <v>81.7</v>
+        <v>293.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1223</v>
+        <v>340</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99919.10000000001</v>
+        <v>99790</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>73.53</v>
+        <v>264.15</v>
       </c>
       <c r="T5" t="n">
-        <v>9991.91</v>
+        <v>9979</v>
       </c>
       <c r="U5" t="n">
-        <v>95.59</v>
+        <v>340.46</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>16986.25</v>
+        <v>15966.4</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>346.95</v>
+        <v>256.35</v>
       </c>
       <c r="E6" t="n">
-        <v>292.63</v>
+        <v>195.41</v>
       </c>
       <c r="F6" t="n">
-        <v>18.56</v>
+        <v>31.19</v>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H6" t="n">
-        <v>57.7</v>
+        <v>19.79</v>
       </c>
       <c r="I6" t="n">
-        <v>46.18</v>
+        <v>67.53</v>
       </c>
       <c r="J6" t="n">
-        <v>3.38</v>
+        <v>5.72</v>
       </c>
       <c r="K6" t="n">
-        <v>66.25</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>79.75</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>346.95</v>
+        <v>256.35</v>
       </c>
       <c r="O6" t="n">
-        <v>288</v>
+        <v>390</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99921.60000000001</v>
+        <v>99976.5</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>312.26</v>
+        <v>230.72</v>
       </c>
       <c r="T6" t="n">
-        <v>9992.16</v>
+        <v>9997.65</v>
       </c>
       <c r="U6" t="n">
-        <v>405.93</v>
+        <v>305.06</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>16986.67</v>
+        <v>18995.54</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEECEE</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>368.65</v>
+        <v>260</v>
       </c>
       <c r="E7" t="n">
-        <v>321.82</v>
+        <v>208.41</v>
       </c>
       <c r="F7" t="n">
-        <v>14.55</v>
+        <v>24.76</v>
       </c>
       <c r="G7" t="n">
-        <v>386</v>
+        <v>241.57</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.49</v>
+        <v>7.63</v>
       </c>
       <c r="I7" t="n">
-        <v>56.44</v>
+        <v>69.34</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>62.5</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>77.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>368.65</v>
+        <v>260</v>
       </c>
       <c r="O7" t="n">
-        <v>271</v>
+        <v>384</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99904.14999999999</v>
+        <v>99840</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S7" t="n">
-        <v>331.78</v>
+        <v>234</v>
       </c>
       <c r="T7" t="n">
-        <v>9990.42</v>
+        <v>9984</v>
       </c>
       <c r="U7" t="n">
-        <v>435.01</v>
+        <v>306.8</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17982.75</v>
+        <v>17971.2</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>666.25</v>
+        <v>584.25</v>
       </c>
       <c r="E8" t="n">
-        <v>532.25</v>
+        <v>490.52</v>
       </c>
       <c r="F8" t="n">
-        <v>25.18</v>
+        <v>19.11</v>
       </c>
       <c r="G8" t="n">
-        <v>675</v>
+        <v>539</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
-        <v>66</v>
+        <v>61.63</v>
       </c>
       <c r="J8" t="n">
-        <v>3.23</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>75.5</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>666.25</v>
+        <v>584.25</v>
       </c>
       <c r="O8" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99937.5</v>
+        <v>99906.75</v>
       </c>
       <c r="R8" t="n">
         <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>599.62</v>
+        <v>525.83</v>
       </c>
       <c r="T8" t="n">
-        <v>9993.75</v>
+        <v>9990.67</v>
       </c>
       <c r="U8" t="n">
-        <v>806.16</v>
+        <v>683.5700000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>20986.88</v>
+        <v>16984.15</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>239.67</v>
+        <v>20.12</v>
       </c>
       <c r="E9" t="n">
-        <v>195.12</v>
+        <v>15.02</v>
       </c>
       <c r="F9" t="n">
-        <v>22.83</v>
+        <v>33.94</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>17.4</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>15.63</v>
       </c>
       <c r="I9" t="n">
-        <v>57.44</v>
+        <v>57.17</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>0.33</v>
       </c>
       <c r="K9" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>74.59999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>239.67</v>
+        <v>20.12</v>
       </c>
       <c r="O9" t="n">
-        <v>417</v>
+        <v>4970</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99942.39</v>
+        <v>99996.39999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>215.7</v>
+        <v>18.11</v>
       </c>
       <c r="T9" t="n">
-        <v>9994.24</v>
+        <v>9999.639999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>285.21</v>
+        <v>23.74</v>
       </c>
       <c r="V9" t="n">
-        <v>19</v>
+        <v>17.99</v>
       </c>
       <c r="W9" t="n">
-        <v>18989.05</v>
+        <v>17989.35</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>588</v>
+        <v>547.1</v>
       </c>
       <c r="E10" t="n">
-        <v>490.06</v>
+        <v>444.23</v>
       </c>
       <c r="F10" t="n">
-        <v>19.99</v>
+        <v>23.16</v>
       </c>
       <c r="G10" t="n">
-        <v>539</v>
+        <v>552.5</v>
       </c>
       <c r="H10" t="n">
-        <v>9.09</v>
+        <v>-0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>63.61</v>
+        <v>48.88</v>
       </c>
       <c r="J10" t="n">
-        <v>0.95</v>
+        <v>1.53</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>62.5</v>
       </c>
       <c r="L10" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M10" t="n">
-        <v>74.34999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="N10" t="n">
-        <v>588</v>
+        <v>547.1</v>
       </c>
       <c r="O10" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99960</v>
+        <v>99572.2</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>529.2</v>
+        <v>492.39</v>
       </c>
       <c r="T10" t="n">
-        <v>9996</v>
+        <v>9957.219999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>687.96</v>
+        <v>645.58</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>16993.2</v>
+        <v>17923</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.86</v>
+        <v>15.06</v>
       </c>
       <c r="E11" t="n">
-        <v>14.97</v>
+        <v>11.78</v>
       </c>
       <c r="F11" t="n">
-        <v>32.64</v>
+        <v>27.89</v>
       </c>
       <c r="G11" t="n">
-        <v>17.4</v>
+        <v>12.8</v>
       </c>
       <c r="H11" t="n">
-        <v>14.14</v>
+        <v>17.66</v>
       </c>
       <c r="I11" t="n">
-        <v>55.21</v>
+        <v>70</v>
       </c>
       <c r="J11" t="n">
-        <v>0.11</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M11" t="n">
-        <v>74.34999999999999</v>
+        <v>74</v>
       </c>
       <c r="N11" t="n">
-        <v>19.86</v>
+        <v>15.06</v>
       </c>
       <c r="O11" t="n">
-        <v>5035</v>
+        <v>6640</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99995.10000000001</v>
+        <v>99998.39999999999</v>
       </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>17.87</v>
+        <v>13.55</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.51</v>
+        <v>9999.84</v>
       </c>
       <c r="U11" t="n">
-        <v>23.43</v>
+        <v>17.92</v>
       </c>
       <c r="V11" t="n">
-        <v>17.98</v>
+        <v>18.99</v>
       </c>
       <c r="W11" t="n">
-        <v>17979.12</v>
+        <v>18989.7</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85.59999999999999</v>
+        <v>327.15</v>
       </c>
       <c r="E2" t="n">
-        <v>72.13</v>
+        <v>239.09</v>
       </c>
       <c r="F2" t="n">
-        <v>18.67</v>
+        <v>36.83</v>
       </c>
       <c r="G2" t="n">
-        <v>58.79</v>
+        <v>220.4</v>
       </c>
       <c r="H2" t="n">
-        <v>45.6</v>
+        <v>48.43</v>
       </c>
       <c r="I2" t="n">
-        <v>65.98999999999999</v>
+        <v>62.54</v>
       </c>
       <c r="J2" t="n">
-        <v>4.38</v>
+        <v>0.43</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>76.75</v>
       </c>
       <c r="N2" t="n">
-        <v>85.59999999999999</v>
+        <v>327.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1168</v>
+        <v>305</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99980.8</v>
+        <v>99780.75</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="S2" t="n">
-        <v>77.04000000000001</v>
+        <v>294.44</v>
       </c>
       <c r="T2" t="n">
-        <v>9998.08</v>
+        <v>9978.08</v>
       </c>
       <c r="U2" t="n">
-        <v>102.72</v>
+        <v>386.04</v>
       </c>
       <c r="V2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W2" t="n">
-        <v>19996.16</v>
+        <v>17960.54</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>213.83</v>
+        <v>1443</v>
       </c>
       <c r="E3" t="n">
-        <v>182.99</v>
+        <v>1353.95</v>
       </c>
       <c r="F3" t="n">
-        <v>16.85</v>
+        <v>6.58</v>
       </c>
       <c r="G3" t="n">
-        <v>205.9</v>
+        <v>1445</v>
       </c>
       <c r="H3" t="n">
-        <v>3.85</v>
+        <v>-0.14</v>
       </c>
       <c r="I3" t="n">
-        <v>69.20999999999999</v>
+        <v>58.55</v>
       </c>
       <c r="J3" t="n">
-        <v>4.29</v>
+        <v>1.25</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="M3" t="n">
-        <v>81.8</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>213.83</v>
+        <v>1443</v>
       </c>
       <c r="O3" t="n">
-        <v>467</v>
+        <v>69</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99858.61</v>
+        <v>99567</v>
       </c>
       <c r="R3" t="n">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>192.45</v>
+        <v>1298.7</v>
       </c>
       <c r="T3" t="n">
-        <v>9985.860000000001</v>
+        <v>9956.700000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>256.6</v>
+        <v>1688.31</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W3" t="n">
-        <v>19971.72</v>
+        <v>16926.39</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11800</v>
+        <v>215</v>
       </c>
       <c r="E4" t="n">
-        <v>8844.74</v>
+        <v>181.56</v>
       </c>
       <c r="F4" t="n">
-        <v>33.41</v>
+        <v>18.42</v>
       </c>
       <c r="G4" t="n">
-        <v>9950</v>
+        <v>135.4</v>
       </c>
       <c r="H4" t="n">
-        <v>18.59</v>
+        <v>58.79</v>
       </c>
       <c r="I4" t="n">
-        <v>56.56</v>
+        <v>59.04</v>
       </c>
       <c r="J4" t="n">
-        <v>1.46</v>
+        <v>4.09</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>76.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>11800</v>
+        <v>215</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>465</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>94400</v>
+        <v>99975</v>
       </c>
       <c r="R4" t="n">
-        <v>9.44</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>10620</v>
+        <v>193.5</v>
       </c>
       <c r="T4" t="n">
-        <v>9440</v>
+        <v>9997.5</v>
       </c>
       <c r="U4" t="n">
-        <v>14042</v>
+        <v>253.7</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>17936</v>
+        <v>17995.5</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>293.5</v>
+        <v>577</v>
       </c>
       <c r="E5" t="n">
-        <v>267.93</v>
+        <v>490.94</v>
       </c>
       <c r="F5" t="n">
-        <v>9.539999999999999</v>
+        <v>17.53</v>
       </c>
       <c r="G5" t="n">
-        <v>290</v>
+        <v>539</v>
       </c>
       <c r="H5" t="n">
-        <v>1.21</v>
+        <v>7.05</v>
       </c>
       <c r="I5" t="n">
-        <v>53.34</v>
+        <v>57.89</v>
       </c>
       <c r="J5" t="n">
-        <v>2.55</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>71.25</v>
+        <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>74.75</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>293.5</v>
+        <v>577</v>
       </c>
       <c r="O5" t="n">
-        <v>340</v>
+        <v>173</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99790</v>
+        <v>99821</v>
       </c>
       <c r="R5" t="n">
         <v>9.98</v>
       </c>
       <c r="S5" t="n">
-        <v>264.15</v>
+        <v>519.3</v>
       </c>
       <c r="T5" t="n">
-        <v>9979</v>
+        <v>9982.1</v>
       </c>
       <c r="U5" t="n">
-        <v>340.46</v>
+        <v>675.09</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W5" t="n">
-        <v>15966.4</v>
+        <v>16969.57</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>256.35</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="n">
-        <v>195.41</v>
+        <v>15.04</v>
       </c>
       <c r="F6" t="n">
-        <v>31.19</v>
+        <v>33.63</v>
       </c>
       <c r="G6" t="n">
-        <v>214</v>
+        <v>17.4</v>
       </c>
       <c r="H6" t="n">
-        <v>19.79</v>
+        <v>15.52</v>
       </c>
       <c r="I6" t="n">
-        <v>67.53</v>
+        <v>56.95</v>
       </c>
       <c r="J6" t="n">
-        <v>5.72</v>
+        <v>0.12</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>256.35</v>
+        <v>20.1</v>
       </c>
       <c r="O6" t="n">
-        <v>390</v>
+        <v>4975</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99976.5</v>
+        <v>99997.5</v>
       </c>
       <c r="R6" t="n">
         <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>230.72</v>
+        <v>18.09</v>
       </c>
       <c r="T6" t="n">
-        <v>9997.65</v>
+        <v>9999.75</v>
       </c>
       <c r="U6" t="n">
-        <v>305.06</v>
+        <v>23.72</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>18.01</v>
       </c>
       <c r="W6" t="n">
-        <v>18995.54</v>
+        <v>18009.55</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>260</v>
+        <v>503</v>
       </c>
       <c r="E7" t="n">
-        <v>208.41</v>
+        <v>306.7</v>
       </c>
       <c r="F7" t="n">
-        <v>24.76</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>241.57</v>
+        <v>298</v>
       </c>
       <c r="H7" t="n">
-        <v>7.63</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>69.34</v>
+        <v>64.22</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="K7" t="n">
         <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M7" t="n">
-        <v>74.34999999999999</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>260</v>
+        <v>503</v>
       </c>
       <c r="O7" t="n">
-        <v>384</v>
+        <v>198</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99840</v>
+        <v>99594</v>
       </c>
       <c r="R7" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>234</v>
+        <v>452.7</v>
       </c>
       <c r="T7" t="n">
-        <v>9984</v>
+        <v>9959.4</v>
       </c>
       <c r="U7" t="n">
-        <v>306.8</v>
+        <v>593.54</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>17971.2</v>
+        <v>17926.92</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>584.25</v>
+        <v>1108.1</v>
       </c>
       <c r="E8" t="n">
-        <v>490.52</v>
+        <v>1053.11</v>
       </c>
       <c r="F8" t="n">
-        <v>19.11</v>
+        <v>5.22</v>
       </c>
       <c r="G8" t="n">
-        <v>539</v>
+        <v>1128.1</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>-1.77</v>
       </c>
       <c r="I8" t="n">
-        <v>61.63</v>
+        <v>53.35</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>1.31</v>
       </c>
       <c r="K8" t="n">
-        <v>61.25</v>
+        <v>63.75</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M8" t="n">
-        <v>74.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="N8" t="n">
-        <v>584.25</v>
+        <v>1108.1</v>
       </c>
       <c r="O8" t="n">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99906.75</v>
+        <v>99729</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>525.83</v>
+        <v>997.29</v>
       </c>
       <c r="T8" t="n">
-        <v>9990.67</v>
+        <v>9972.9</v>
       </c>
       <c r="U8" t="n">
-        <v>683.5700000000001</v>
+        <v>1263.23</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>16984.15</v>
+        <v>13962.06</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.12</v>
+        <v>544.55</v>
       </c>
       <c r="E9" t="n">
-        <v>15.02</v>
+        <v>444.66</v>
       </c>
       <c r="F9" t="n">
-        <v>33.94</v>
+        <v>22.46</v>
       </c>
       <c r="G9" t="n">
-        <v>17.4</v>
+        <v>552.5</v>
       </c>
       <c r="H9" t="n">
-        <v>15.63</v>
+        <v>-1.44</v>
       </c>
       <c r="I9" t="n">
-        <v>57.17</v>
+        <v>48.17</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33</v>
+        <v>1.22</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>58.75</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>72.05</v>
       </c>
       <c r="N9" t="n">
-        <v>20.12</v>
+        <v>544.55</v>
       </c>
       <c r="O9" t="n">
-        <v>4970</v>
+        <v>183</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99996.39999999999</v>
+        <v>99652.64999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>18.11</v>
+        <v>490.1</v>
       </c>
       <c r="T9" t="n">
-        <v>9999.639999999999</v>
+        <v>9965.26</v>
       </c>
       <c r="U9" t="n">
-        <v>23.74</v>
+        <v>631.6799999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>17.99</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>17989.35</v>
+        <v>15944.42</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>547.1</v>
+        <v>1291.15</v>
       </c>
       <c r="E10" t="n">
-        <v>444.23</v>
+        <v>930.46</v>
       </c>
       <c r="F10" t="n">
-        <v>23.16</v>
+        <v>38.76</v>
       </c>
       <c r="G10" t="n">
-        <v>552.5</v>
+        <v>993.8</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.98</v>
+        <v>29.92</v>
       </c>
       <c r="I10" t="n">
-        <v>48.88</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.53</v>
+        <v>0.33</v>
       </c>
       <c r="K10" t="n">
-        <v>62.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M10" t="n">
-        <v>74.3</v>
+        <v>71.95</v>
       </c>
       <c r="N10" t="n">
-        <v>547.1</v>
+        <v>1291.15</v>
       </c>
       <c r="O10" t="n">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99572.2</v>
+        <v>99418.55</v>
       </c>
       <c r="R10" t="n">
-        <v>9.960000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>492.39</v>
+        <v>1162.04</v>
       </c>
       <c r="T10" t="n">
-        <v>9957.219999999999</v>
+        <v>9941.860000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>645.58</v>
+        <v>1523.56</v>
       </c>
       <c r="V10" t="n">
         <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>17923</v>
+        <v>17895.34</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.06</v>
+        <v>1091</v>
       </c>
       <c r="E11" t="n">
-        <v>11.78</v>
+        <v>993.4299999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>27.89</v>
+        <v>9.82</v>
       </c>
       <c r="G11" t="n">
-        <v>12.8</v>
+        <v>1039.2</v>
       </c>
       <c r="H11" t="n">
-        <v>17.66</v>
+        <v>4.98</v>
       </c>
       <c r="I11" t="n">
-        <v>70</v>
+        <v>54.57</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>0.52</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>57.5</v>
       </c>
       <c r="L11" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>71.3</v>
       </c>
       <c r="N11" t="n">
-        <v>15.06</v>
+        <v>1091</v>
       </c>
       <c r="O11" t="n">
-        <v>6640</v>
+        <v>91</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99998.39999999999</v>
+        <v>99281</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="S11" t="n">
-        <v>13.55</v>
+        <v>981.9</v>
       </c>
       <c r="T11" t="n">
-        <v>9999.84</v>
+        <v>9928.1</v>
       </c>
       <c r="U11" t="n">
-        <v>17.92</v>
+        <v>1232.83</v>
       </c>
       <c r="V11" t="n">
-        <v>18.99</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>18989.7</v>
+        <v>12906.53</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,73 +549,73 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SANGHVIMOV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>327.15</v>
+        <v>457.25</v>
       </c>
       <c r="E2" t="n">
-        <v>239.09</v>
+        <v>349.51</v>
       </c>
       <c r="F2" t="n">
-        <v>36.83</v>
+        <v>30.83</v>
       </c>
       <c r="G2" t="n">
-        <v>220.4</v>
+        <v>411.9</v>
       </c>
       <c r="H2" t="n">
-        <v>48.43</v>
+        <v>11.01</v>
       </c>
       <c r="I2" t="n">
-        <v>62.54</v>
+        <v>47.13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.43</v>
+        <v>0.82</v>
       </c>
       <c r="K2" t="n">
-        <v>61.25</v>
+        <v>52.5</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>76.75</v>
+        <v>71.5</v>
       </c>
       <c r="N2" t="n">
-        <v>327.15</v>
+        <v>457.25</v>
       </c>
       <c r="O2" t="n">
-        <v>305</v>
+        <v>218</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99780.75</v>
+        <v>99680.5</v>
       </c>
       <c r="R2" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>294.44</v>
+        <v>411.52</v>
       </c>
       <c r="T2" t="n">
-        <v>9978.08</v>
+        <v>9968.049999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>386.04</v>
+        <v>525.84</v>
       </c>
       <c r="V2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>17960.54</v>
+        <v>14952.08</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1443</v>
+        <v>701.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1353.95</v>
+        <v>544.09</v>
       </c>
       <c r="F3" t="n">
-        <v>6.58</v>
+        <v>28.99</v>
       </c>
       <c r="G3" t="n">
-        <v>1445</v>
+        <v>659.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.14</v>
+        <v>6.46</v>
       </c>
       <c r="I3" t="n">
-        <v>58.55</v>
+        <v>46.62</v>
       </c>
       <c r="J3" t="n">
-        <v>1.25</v>
+        <v>0.47</v>
       </c>
       <c r="K3" t="n">
-        <v>68.75</v>
+        <v>52.5</v>
       </c>
       <c r="L3" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>74.84999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1443</v>
+        <v>701.8</v>
       </c>
       <c r="O3" t="n">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99567</v>
+        <v>99655.60000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1298.7</v>
+        <v>631.62</v>
       </c>
       <c r="T3" t="n">
-        <v>9956.700000000001</v>
+        <v>9965.559999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1688.31</v>
+        <v>807.0700000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
-        <v>16926.39</v>
+        <v>14948.34</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>PANAMAPET</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>215</v>
+        <v>471.35</v>
       </c>
       <c r="E4" t="n">
-        <v>181.56</v>
+        <v>336.22</v>
       </c>
       <c r="F4" t="n">
-        <v>18.42</v>
+        <v>40.19</v>
       </c>
       <c r="G4" t="n">
-        <v>135.4</v>
+        <v>342.2</v>
       </c>
       <c r="H4" t="n">
-        <v>58.79</v>
+        <v>37.74</v>
       </c>
       <c r="I4" t="n">
-        <v>59.04</v>
+        <v>48.97</v>
       </c>
       <c r="J4" t="n">
-        <v>4.09</v>
+        <v>0.18</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>52.5</v>
       </c>
       <c r="L4" t="n">
         <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>74.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>471.35</v>
       </c>
       <c r="O4" t="n">
-        <v>465</v>
+        <v>212</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99975</v>
+        <v>99926.2</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>193.5</v>
+        <v>424.22</v>
       </c>
       <c r="T4" t="n">
-        <v>9997.5</v>
+        <v>9992.620000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>253.7</v>
+        <v>532.63</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>17995.5</v>
+        <v>12990.41</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>577</v>
+        <v>1979.2</v>
       </c>
       <c r="E5" t="n">
-        <v>490.94</v>
+        <v>1518.8</v>
       </c>
       <c r="F5" t="n">
-        <v>17.53</v>
+        <v>30.31</v>
       </c>
       <c r="G5" t="n">
-        <v>539</v>
+        <v>1680</v>
       </c>
       <c r="H5" t="n">
-        <v>7.05</v>
+        <v>17.81</v>
       </c>
       <c r="I5" t="n">
-        <v>57.89</v>
+        <v>47.98</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>1.28</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>74.34999999999999</v>
+        <v>59.15</v>
       </c>
       <c r="N5" t="n">
-        <v>577</v>
+        <v>1979.2</v>
       </c>
       <c r="O5" t="n">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99821</v>
+        <v>98960</v>
       </c>
       <c r="R5" t="n">
-        <v>9.98</v>
+        <v>9.9</v>
       </c>
       <c r="S5" t="n">
-        <v>519.3</v>
+        <v>1781.28</v>
       </c>
       <c r="T5" t="n">
-        <v>9982.1</v>
+        <v>9896</v>
       </c>
       <c r="U5" t="n">
-        <v>675.09</v>
+        <v>2196.91</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>16969.57</v>
+        <v>10885.6</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>RPGLIFE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>2629</v>
       </c>
       <c r="E6" t="n">
-        <v>15.04</v>
+        <v>2267.07</v>
       </c>
       <c r="F6" t="n">
-        <v>33.63</v>
+        <v>15.96</v>
       </c>
       <c r="G6" t="n">
-        <v>17.4</v>
+        <v>2524.9</v>
       </c>
       <c r="H6" t="n">
-        <v>15.52</v>
+        <v>4.12</v>
       </c>
       <c r="I6" t="n">
-        <v>56.95</v>
+        <v>46.1</v>
       </c>
       <c r="J6" t="n">
-        <v>0.12</v>
+        <v>1.65</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>63.75</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>74.34999999999999</v>
+        <v>58.25</v>
       </c>
       <c r="N6" t="n">
-        <v>20.1</v>
+        <v>2629</v>
       </c>
       <c r="O6" t="n">
-        <v>4975</v>
+        <v>38</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99997.5</v>
+        <v>99902</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>18.09</v>
+        <v>2366.1</v>
       </c>
       <c r="T6" t="n">
-        <v>9999.75</v>
+        <v>9990.200000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>23.72</v>
+        <v>2944.48</v>
       </c>
       <c r="V6" t="n">
-        <v>18.01</v>
+        <v>12</v>
       </c>
       <c r="W6" t="n">
-        <v>18009.55</v>
+        <v>11988.24</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDOBORAX</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>2859.1</v>
       </c>
       <c r="E7" t="n">
-        <v>306.7</v>
+        <v>2506.43</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>14.07</v>
       </c>
       <c r="G7" t="n">
-        <v>298</v>
+        <v>2695</v>
       </c>
       <c r="H7" t="n">
-        <v>68.79000000000001</v>
+        <v>6.09</v>
       </c>
       <c r="I7" t="n">
-        <v>64.22</v>
+        <v>35.22</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2</v>
+        <v>7.52</v>
       </c>
       <c r="K7" t="n">
         <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
-        <v>72.34999999999999</v>
+        <v>54.75</v>
       </c>
       <c r="N7" t="n">
-        <v>503</v>
+        <v>2859.1</v>
       </c>
       <c r="O7" t="n">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99594</v>
+        <v>97209.39999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.960000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>452.7</v>
+        <v>2573.19</v>
       </c>
       <c r="T7" t="n">
-        <v>9959.4</v>
+        <v>9720.940000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>593.54</v>
+        <v>3202.19</v>
       </c>
       <c r="V7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W7" t="n">
-        <v>17926.92</v>
+        <v>11665.13</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>VISAKAIND</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1108.1</v>
+        <v>88.53</v>
       </c>
       <c r="E8" t="n">
-        <v>1053.11</v>
+        <v>71.48</v>
       </c>
       <c r="F8" t="n">
-        <v>5.22</v>
+        <v>23.85</v>
       </c>
       <c r="G8" t="n">
-        <v>1128.1</v>
+        <v>88.25</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.77</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>53.35</v>
+        <v>46.67</v>
       </c>
       <c r="J8" t="n">
-        <v>1.31</v>
+        <v>0.23</v>
       </c>
       <c r="K8" t="n">
-        <v>63.75</v>
+        <v>52.5</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>72.25</v>
+        <v>51.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1108.1</v>
+        <v>88.53</v>
       </c>
       <c r="O8" t="n">
-        <v>90</v>
+        <v>1129</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99729</v>
+        <v>99950.37</v>
       </c>
       <c r="R8" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>997.29</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>9972.9</v>
+        <v>9995.040000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>1263.23</v>
+        <v>97.38</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>13962.06</v>
+        <v>9995.040000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>544.55</v>
+        <v>75.17</v>
       </c>
       <c r="E9" t="n">
-        <v>444.66</v>
+        <v>52.69</v>
       </c>
       <c r="F9" t="n">
-        <v>22.46</v>
+        <v>42.66</v>
       </c>
       <c r="G9" t="n">
-        <v>552.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.44</v>
+        <v>13.72</v>
       </c>
       <c r="I9" t="n">
-        <v>48.17</v>
+        <v>46.11</v>
       </c>
       <c r="J9" t="n">
-        <v>1.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>58.75</v>
+        <v>52.5</v>
       </c>
       <c r="L9" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="M9" t="n">
-        <v>72.05</v>
+        <v>48.3</v>
       </c>
       <c r="N9" t="n">
-        <v>544.55</v>
+        <v>75.17</v>
       </c>
       <c r="O9" t="n">
-        <v>183</v>
+        <v>1330</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99652.64999999999</v>
+        <v>99976.10000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>490.1</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>9965.26</v>
+        <v>9997.610000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>631.6799999999999</v>
+        <v>82.69</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>15944.42</v>
+        <v>9997.610000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1291.15</v>
+        <v>2104.9</v>
       </c>
       <c r="E10" t="n">
-        <v>930.46</v>
+        <v>1795.06</v>
       </c>
       <c r="F10" t="n">
-        <v>38.76</v>
+        <v>17.26</v>
       </c>
       <c r="G10" t="n">
-        <v>993.8</v>
+        <v>1362.1</v>
       </c>
       <c r="H10" t="n">
-        <v>29.92</v>
+        <v>54.53</v>
       </c>
       <c r="I10" t="n">
-        <v>65.15000000000001</v>
+        <v>51.07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>57.5</v>
       </c>
       <c r="L10" t="n">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="M10" t="n">
-        <v>71.95</v>
+        <v>45.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1291.15</v>
+        <v>2104.9</v>
       </c>
       <c r="O10" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99418.55</v>
+        <v>98930.3</v>
       </c>
       <c r="R10" t="n">
-        <v>9.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1162.04</v>
+        <v>1894.41</v>
       </c>
       <c r="T10" t="n">
-        <v>9941.860000000001</v>
+        <v>9893.030000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1523.56</v>
+        <v>2294.34</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>17895.34</v>
+        <v>8903.73</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1091</v>
+        <v>1717</v>
       </c>
       <c r="E11" t="n">
-        <v>993.4299999999999</v>
+        <v>1364.5</v>
       </c>
       <c r="F11" t="n">
-        <v>9.82</v>
+        <v>25.83</v>
       </c>
       <c r="G11" t="n">
-        <v>1039.2</v>
+        <v>1270.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.98</v>
+        <v>35.11</v>
       </c>
       <c r="I11" t="n">
-        <v>54.57</v>
+        <v>68.33</v>
       </c>
       <c r="J11" t="n">
-        <v>0.52</v>
+        <v>2.21</v>
       </c>
       <c r="K11" t="n">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>71.3</v>
+        <v>45</v>
       </c>
       <c r="N11" t="n">
-        <v>1091</v>
+        <v>1717</v>
       </c>
       <c r="O11" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99281</v>
+        <v>99586</v>
       </c>
       <c r="R11" t="n">
-        <v>9.93</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>981.9</v>
+        <v>1545.3</v>
       </c>
       <c r="T11" t="n">
-        <v>9928.1</v>
+        <v>9958.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1232.83</v>
+        <v>1991.72</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>12906.53</v>
+        <v>15933.76</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH RISK</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANGHVIMOV</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>457.25</v>
+        <v>127.16</v>
       </c>
       <c r="E2" t="n">
-        <v>349.51</v>
+        <v>96.33</v>
       </c>
       <c r="F2" t="n">
-        <v>30.83</v>
+        <v>32.01</v>
       </c>
       <c r="G2" t="n">
-        <v>411.9</v>
+        <v>108.59</v>
       </c>
       <c r="H2" t="n">
-        <v>11.01</v>
+        <v>17.1</v>
       </c>
       <c r="I2" t="n">
-        <v>47.13</v>
+        <v>57.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0.82</v>
+        <v>2.1</v>
       </c>
       <c r="K2" t="n">
-        <v>52.5</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M2" t="n">
-        <v>71.5</v>
+        <v>81.8</v>
       </c>
       <c r="N2" t="n">
-        <v>457.25</v>
+        <v>127.16</v>
       </c>
       <c r="O2" t="n">
-        <v>218</v>
+        <v>786</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99680.5</v>
+        <v>99947.75999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S2" t="n">
-        <v>411.52</v>
+        <v>114.44</v>
       </c>
       <c r="T2" t="n">
-        <v>9968.049999999999</v>
+        <v>9994.780000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>525.84</v>
+        <v>153.86</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>14952.08</v>
+        <v>20989.03</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>IMPAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>701.8</v>
+        <v>1131.4</v>
       </c>
       <c r="E3" t="n">
-        <v>544.09</v>
+        <v>1053.68</v>
       </c>
       <c r="F3" t="n">
-        <v>28.99</v>
+        <v>7.38</v>
       </c>
       <c r="G3" t="n">
-        <v>659.2</v>
+        <v>1128.1</v>
       </c>
       <c r="H3" t="n">
-        <v>6.46</v>
+        <v>0.29</v>
       </c>
       <c r="I3" t="n">
-        <v>46.62</v>
+        <v>57.38</v>
       </c>
       <c r="J3" t="n">
-        <v>0.47</v>
+        <v>3.93</v>
       </c>
       <c r="K3" t="n">
-        <v>52.5</v>
+        <v>75</v>
       </c>
       <c r="L3" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M3" t="n">
-        <v>69.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="N3" t="n">
-        <v>701.8</v>
+        <v>1131.4</v>
       </c>
       <c r="O3" t="n">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99655.60000000001</v>
+        <v>99563.2</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>631.62</v>
+        <v>1018.26</v>
       </c>
       <c r="T3" t="n">
-        <v>9965.559999999999</v>
+        <v>9956.32</v>
       </c>
       <c r="U3" t="n">
-        <v>807.0700000000001</v>
+        <v>1346.37</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>14948.34</v>
+        <v>18917.01</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,77 +719,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PANAMAPET</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>471.35</v>
+        <v>82.7</v>
       </c>
       <c r="E4" t="n">
-        <v>336.22</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>40.19</v>
+        <v>13.83</v>
       </c>
       <c r="G4" t="n">
-        <v>342.2</v>
+        <v>58.79</v>
       </c>
       <c r="H4" t="n">
-        <v>37.74</v>
+        <v>40.67</v>
       </c>
       <c r="I4" t="n">
-        <v>48.97</v>
+        <v>53.85</v>
       </c>
       <c r="J4" t="n">
-        <v>0.18</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>52.5</v>
+        <v>62.5</v>
       </c>
       <c r="L4" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>61.1</v>
+        <v>77.5</v>
       </c>
       <c r="N4" t="n">
-        <v>471.35</v>
+        <v>82.7</v>
       </c>
       <c r="O4" t="n">
-        <v>212</v>
+        <v>1209</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99926.2</v>
+        <v>99984.3</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S4" t="n">
-        <v>424.22</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>9992.620000000001</v>
+        <v>9998.43</v>
       </c>
       <c r="U4" t="n">
-        <v>532.63</v>
+        <v>94.28</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
-        <v>12990.41</v>
+        <v>13997.8</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -804,77 +804,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1979.2</v>
+        <v>330.9</v>
       </c>
       <c r="E5" t="n">
-        <v>1518.8</v>
+        <v>241.42</v>
       </c>
       <c r="F5" t="n">
-        <v>30.31</v>
+        <v>37.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1680</v>
+        <v>220.4</v>
       </c>
       <c r="H5" t="n">
-        <v>17.81</v>
+        <v>50.14</v>
       </c>
       <c r="I5" t="n">
-        <v>47.98</v>
+        <v>62.61</v>
       </c>
       <c r="J5" t="n">
-        <v>1.28</v>
+        <v>0.48</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>59.15</v>
+        <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1979.2</v>
+        <v>330.9</v>
       </c>
       <c r="O5" t="n">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>98960</v>
+        <v>99931.8</v>
       </c>
       <c r="R5" t="n">
-        <v>9.9</v>
+        <v>9.99</v>
       </c>
       <c r="S5" t="n">
-        <v>1781.28</v>
+        <v>297.81</v>
       </c>
       <c r="T5" t="n">
-        <v>9896</v>
+        <v>9993.18</v>
       </c>
       <c r="U5" t="n">
-        <v>2196.91</v>
+        <v>390.46</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>10885.6</v>
+        <v>17987.72</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -889,77 +889,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RPGLIFE</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2629</v>
+        <v>224.39</v>
       </c>
       <c r="E6" t="n">
-        <v>2267.07</v>
+        <v>183.93</v>
       </c>
       <c r="F6" t="n">
-        <v>15.96</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>2524.9</v>
+        <v>205.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.12</v>
+        <v>8.98</v>
       </c>
       <c r="I6" t="n">
-        <v>46.1</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="K6" t="n">
-        <v>63.75</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>58.25</v>
+        <v>75.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2629</v>
+        <v>224.39</v>
       </c>
       <c r="O6" t="n">
-        <v>38</v>
+        <v>445</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99902</v>
+        <v>99853.55</v>
       </c>
       <c r="R6" t="n">
         <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>2366.1</v>
+        <v>201.95</v>
       </c>
       <c r="T6" t="n">
-        <v>9990.200000000001</v>
+        <v>9985.360000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>2944.48</v>
+        <v>260.29</v>
       </c>
       <c r="V6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W6" t="n">
-        <v>11988.24</v>
+        <v>15976.57</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -974,77 +974,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2859.1</v>
+        <v>2711.2</v>
       </c>
       <c r="E7" t="n">
-        <v>2506.43</v>
+        <v>2033.19</v>
       </c>
       <c r="F7" t="n">
-        <v>14.07</v>
+        <v>33.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2695</v>
+        <v>2602</v>
       </c>
       <c r="H7" t="n">
-        <v>6.09</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.22</v>
+        <v>63.64</v>
       </c>
       <c r="J7" t="n">
-        <v>7.52</v>
+        <v>10.46</v>
       </c>
       <c r="K7" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="M7" t="n">
-        <v>54.75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>2859.1</v>
+        <v>2711.2</v>
       </c>
       <c r="O7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>97209.39999999999</v>
+        <v>97603.2</v>
       </c>
       <c r="R7" t="n">
-        <v>9.720000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="S7" t="n">
-        <v>2573.19</v>
+        <v>2440.08</v>
       </c>
       <c r="T7" t="n">
-        <v>9720.940000000001</v>
+        <v>9760.32</v>
       </c>
       <c r="U7" t="n">
-        <v>3202.19</v>
+        <v>3226.33</v>
       </c>
       <c r="V7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>11665.13</v>
+        <v>18544.61</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1059,77 +1059,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VISAKAIND</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>88.53</v>
+        <v>234.99</v>
       </c>
       <c r="E8" t="n">
-        <v>71.48</v>
+        <v>205.24</v>
       </c>
       <c r="F8" t="n">
-        <v>23.85</v>
+        <v>14.5</v>
       </c>
       <c r="G8" t="n">
-        <v>88.25</v>
+        <v>245.38</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>-4.23</v>
       </c>
       <c r="I8" t="n">
-        <v>46.67</v>
+        <v>62.18</v>
       </c>
       <c r="J8" t="n">
-        <v>0.23</v>
+        <v>1.08</v>
       </c>
       <c r="K8" t="n">
-        <v>52.5</v>
+        <v>58.75</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>51.5</v>
+        <v>75.25</v>
       </c>
       <c r="N8" t="n">
-        <v>88.53</v>
+        <v>234.99</v>
       </c>
       <c r="O8" t="n">
-        <v>1129</v>
+        <v>425</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99950.37</v>
+        <v>99870.75</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>79.68000000000001</v>
+        <v>211.49</v>
       </c>
       <c r="T8" t="n">
-        <v>9995.040000000001</v>
+        <v>9987.08</v>
       </c>
       <c r="U8" t="n">
-        <v>97.38</v>
+        <v>274.94</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>9995.040000000001</v>
+        <v>16978.03</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1144,77 +1144,77 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75.17</v>
+        <v>576</v>
       </c>
       <c r="E9" t="n">
-        <v>52.69</v>
+        <v>491.89</v>
       </c>
       <c r="F9" t="n">
-        <v>42.66</v>
+        <v>17.1</v>
       </c>
       <c r="G9" t="n">
-        <v>66.09999999999999</v>
+        <v>539</v>
       </c>
       <c r="H9" t="n">
-        <v>13.72</v>
+        <v>6.86</v>
       </c>
       <c r="I9" t="n">
-        <v>46.11</v>
+        <v>56.73</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="K9" t="n">
-        <v>52.5</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="M9" t="n">
-        <v>48.3</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>75.17</v>
+        <v>576</v>
       </c>
       <c r="O9" t="n">
-        <v>1330</v>
+        <v>173</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99976.10000000001</v>
+        <v>99648</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>67.65000000000001</v>
+        <v>518.4</v>
       </c>
       <c r="T9" t="n">
-        <v>9997.610000000001</v>
+        <v>9964.799999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>82.69</v>
+        <v>673.92</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="W9" t="n">
-        <v>9997.610000000001</v>
+        <v>16940.16</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1229,77 +1229,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2104.9</v>
+        <v>249.74</v>
       </c>
       <c r="E10" t="n">
-        <v>1795.06</v>
+        <v>208.99</v>
       </c>
       <c r="F10" t="n">
-        <v>17.26</v>
+        <v>19.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1362.1</v>
+        <v>241.57</v>
       </c>
       <c r="H10" t="n">
-        <v>54.53</v>
+        <v>3.38</v>
       </c>
       <c r="I10" t="n">
-        <v>51.07</v>
+        <v>58.03</v>
       </c>
       <c r="J10" t="n">
-        <v>0.59</v>
+        <v>0.24</v>
       </c>
       <c r="K10" t="n">
-        <v>57.5</v>
+        <v>61.25</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="M10" t="n">
-        <v>45.7</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>2104.9</v>
+        <v>249.74</v>
       </c>
       <c r="O10" t="n">
-        <v>47</v>
+        <v>400</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>98930.3</v>
+        <v>99896</v>
       </c>
       <c r="R10" t="n">
-        <v>9.890000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S10" t="n">
-        <v>1894.41</v>
+        <v>224.77</v>
       </c>
       <c r="T10" t="n">
-        <v>9893.030000000001</v>
+        <v>9989.6</v>
       </c>
       <c r="U10" t="n">
-        <v>2294.34</v>
+        <v>292.2</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>8903.73</v>
+        <v>16982.32</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1314,77 +1314,77 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1717</v>
+        <v>140.6</v>
       </c>
       <c r="E11" t="n">
-        <v>1364.5</v>
+        <v>93.98</v>
       </c>
       <c r="F11" t="n">
-        <v>25.83</v>
+        <v>49.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1270.8</v>
+        <v>114</v>
       </c>
       <c r="H11" t="n">
-        <v>35.11</v>
+        <v>23.33</v>
       </c>
       <c r="I11" t="n">
-        <v>68.33</v>
+        <v>84.72</v>
       </c>
       <c r="J11" t="n">
-        <v>2.21</v>
+        <v>10.69</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M11" t="n">
-        <v>45</v>
+        <v>73.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1717</v>
+        <v>140.6</v>
       </c>
       <c r="O11" t="n">
-        <v>58</v>
+        <v>711</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99586</v>
+        <v>99966.60000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>1545.3</v>
+        <v>126.54</v>
       </c>
       <c r="T11" t="n">
-        <v>9958.6</v>
+        <v>9996.66</v>
       </c>
       <c r="U11" t="n">
-        <v>1991.72</v>
+        <v>163.1</v>
       </c>
       <c r="V11" t="n">
         <v>16</v>
       </c>
       <c r="W11" t="n">
-        <v>15933.76</v>
+        <v>15994.66</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>HIGH RISK</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>127.16</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>96.33</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>32.01</v>
+        <v>13.24</v>
       </c>
       <c r="G2" t="n">
-        <v>108.59</v>
+        <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>17.1</v>
+        <v>40.16</v>
       </c>
       <c r="I2" t="n">
-        <v>57.75</v>
+        <v>52.72</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>66.25</v>
       </c>
       <c r="L2" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>81.8</v>
+        <v>79.75</v>
       </c>
       <c r="N2" t="n">
-        <v>127.16</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>786</v>
+        <v>1213</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99947.75999999999</v>
+        <v>99951.2</v>
       </c>
       <c r="R2" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>114.44</v>
+        <v>74.16</v>
       </c>
       <c r="T2" t="n">
-        <v>9994.780000000001</v>
+        <v>9995.120000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>153.86</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>20989.03</v>
+        <v>14992.68</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,73 +634,73 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IMPAL</t>
+          <t>UFLEX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1131.4</v>
+        <v>701.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1053.68</v>
+        <v>461.11</v>
       </c>
       <c r="F3" t="n">
-        <v>7.38</v>
+        <v>52.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1128.1</v>
+        <v>685.6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.29</v>
+        <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>57.38</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.93</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L3" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>79</v>
+        <v>76.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1131.4</v>
+        <v>701.8</v>
       </c>
       <c r="O3" t="n">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99563.2</v>
+        <v>99655.60000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1018.26</v>
+        <v>631.62</v>
       </c>
       <c r="T3" t="n">
-        <v>9956.32</v>
+        <v>9965.559999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>1346.37</v>
+        <v>814.09</v>
       </c>
       <c r="V3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>18917.01</v>
+        <v>15944.9</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CORDSCABLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.7</v>
+        <v>315.5</v>
       </c>
       <c r="E4" t="n">
-        <v>72.65000000000001</v>
+        <v>192.52</v>
       </c>
       <c r="F4" t="n">
-        <v>13.83</v>
+        <v>63.88</v>
       </c>
       <c r="G4" t="n">
-        <v>58.79</v>
+        <v>216.6</v>
       </c>
       <c r="H4" t="n">
-        <v>40.67</v>
+        <v>45.66</v>
       </c>
       <c r="I4" t="n">
-        <v>53.85</v>
+        <v>83.53</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>3.28</v>
       </c>
       <c r="K4" t="n">
-        <v>62.5</v>
+        <v>61.25</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>77.5</v>
+        <v>76.75</v>
       </c>
       <c r="N4" t="n">
-        <v>82.7</v>
+        <v>315.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1209</v>
+        <v>316</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99984.3</v>
+        <v>99698</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>74.43000000000001</v>
+        <v>283.95</v>
       </c>
       <c r="T4" t="n">
-        <v>9998.43</v>
+        <v>9969.799999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>94.28</v>
+        <v>365.98</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W4" t="n">
-        <v>13997.8</v>
+        <v>15951.68</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,34 +804,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MODISONLTD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>330.9</v>
+        <v>520.65</v>
       </c>
       <c r="E5" t="n">
-        <v>241.42</v>
+        <v>209.44</v>
       </c>
       <c r="F5" t="n">
-        <v>37.06</v>
+        <v>148.6</v>
       </c>
       <c r="G5" t="n">
-        <v>220.4</v>
+        <v>197.45</v>
       </c>
       <c r="H5" t="n">
-        <v>50.14</v>
+        <v>163.69</v>
       </c>
       <c r="I5" t="n">
-        <v>62.61</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.48</v>
+        <v>3.61</v>
       </c>
       <c r="K5" t="n">
         <v>61.25</v>
@@ -843,34 +843,34 @@
         <v>76.75</v>
       </c>
       <c r="N5" t="n">
-        <v>330.9</v>
+        <v>520.65</v>
       </c>
       <c r="O5" t="n">
-        <v>302</v>
+        <v>192</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99931.8</v>
+        <v>99964.8</v>
       </c>
       <c r="R5" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>297.81</v>
+        <v>468.58</v>
       </c>
       <c r="T5" t="n">
-        <v>9993.18</v>
+        <v>9996.48</v>
       </c>
       <c r="U5" t="n">
-        <v>390.46</v>
+        <v>603.95</v>
       </c>
       <c r="V5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W5" t="n">
-        <v>17987.72</v>
+        <v>15994.37</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>224.39</v>
+        <v>330.35</v>
       </c>
       <c r="E6" t="n">
-        <v>183.93</v>
+        <v>242.2</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>36.4</v>
       </c>
       <c r="G6" t="n">
-        <v>205.9</v>
+        <v>220.4</v>
       </c>
       <c r="H6" t="n">
-        <v>8.98</v>
+        <v>49.89</v>
       </c>
       <c r="I6" t="n">
-        <v>71.73999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>61.25</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>75.8</v>
+        <v>76.75</v>
       </c>
       <c r="N6" t="n">
-        <v>224.39</v>
+        <v>330.35</v>
       </c>
       <c r="O6" t="n">
-        <v>445</v>
+        <v>302</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99853.55</v>
+        <v>99765.7</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S6" t="n">
-        <v>201.95</v>
+        <v>297.32</v>
       </c>
       <c r="T6" t="n">
-        <v>9985.360000000001</v>
+        <v>9976.57</v>
       </c>
       <c r="U6" t="n">
-        <v>260.29</v>
+        <v>389.81</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W6" t="n">
-        <v>15976.57</v>
+        <v>17957.83</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,34 +974,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2711.2</v>
+        <v>602.35</v>
       </c>
       <c r="E7" t="n">
-        <v>2033.19</v>
+        <v>475.47</v>
       </c>
       <c r="F7" t="n">
-        <v>33.35</v>
+        <v>26.69</v>
       </c>
       <c r="G7" t="n">
-        <v>2602</v>
+        <v>520.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>15.7</v>
       </c>
       <c r="I7" t="n">
-        <v>63.64</v>
+        <v>63.55</v>
       </c>
       <c r="J7" t="n">
-        <v>10.46</v>
+        <v>18.27</v>
       </c>
       <c r="K7" t="n">
         <v>75</v>
@@ -1013,34 +1013,34 @@
         <v>75.40000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>2711.2</v>
+        <v>602.35</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>97603.2</v>
+        <v>99990.10000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>9.76</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>2440.08</v>
+        <v>542.12</v>
       </c>
       <c r="T7" t="n">
-        <v>9760.32</v>
+        <v>9999.01</v>
       </c>
       <c r="U7" t="n">
-        <v>3226.33</v>
+        <v>716.8</v>
       </c>
       <c r="V7" t="n">
         <v>19</v>
       </c>
       <c r="W7" t="n">
-        <v>18544.61</v>
+        <v>18998.12</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,34 +1059,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>TNPETRO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>234.99</v>
+        <v>133.73</v>
       </c>
       <c r="E8" t="n">
-        <v>205.24</v>
+        <v>95.86</v>
       </c>
       <c r="F8" t="n">
-        <v>14.5</v>
+        <v>39.51</v>
       </c>
       <c r="G8" t="n">
-        <v>245.38</v>
+        <v>129.89</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.23</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>62.18</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.08</v>
+        <v>1.79</v>
       </c>
       <c r="K8" t="n">
         <v>58.75</v>
@@ -1098,34 +1098,34 @@
         <v>75.25</v>
       </c>
       <c r="N8" t="n">
-        <v>234.99</v>
+        <v>133.73</v>
       </c>
       <c r="O8" t="n">
-        <v>425</v>
+        <v>747</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99870.75</v>
+        <v>99896.31</v>
       </c>
       <c r="R8" t="n">
         <v>9.99</v>
       </c>
       <c r="S8" t="n">
-        <v>211.49</v>
+        <v>120.36</v>
       </c>
       <c r="T8" t="n">
-        <v>9987.08</v>
+        <v>9989.629999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>274.94</v>
+        <v>155.13</v>
       </c>
       <c r="V8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>16978.03</v>
+        <v>15983.41</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>576</v>
+        <v>12158</v>
       </c>
       <c r="E9" t="n">
-        <v>491.89</v>
+        <v>8942.139999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>17.1</v>
+        <v>35.96</v>
       </c>
       <c r="G9" t="n">
-        <v>539</v>
+        <v>9950</v>
       </c>
       <c r="H9" t="n">
-        <v>6.86</v>
+        <v>22.19</v>
       </c>
       <c r="I9" t="n">
-        <v>56.73</v>
+        <v>59.12</v>
       </c>
       <c r="J9" t="n">
-        <v>0.55</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L9" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>74.34999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="N9" t="n">
-        <v>576</v>
+        <v>12158</v>
       </c>
       <c r="O9" t="n">
-        <v>173</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99648</v>
+        <v>97264</v>
       </c>
       <c r="R9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="S9" t="n">
-        <v>518.4</v>
+        <v>10942.2</v>
       </c>
       <c r="T9" t="n">
-        <v>9964.799999999999</v>
+        <v>9726.4</v>
       </c>
       <c r="U9" t="n">
-        <v>673.92</v>
+        <v>14346.44</v>
       </c>
       <c r="V9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W9" t="n">
-        <v>16940.16</v>
+        <v>17507.52</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1234,29 +1234,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>249.74</v>
+        <v>253.7</v>
       </c>
       <c r="E10" t="n">
-        <v>208.99</v>
+        <v>209.14</v>
       </c>
       <c r="F10" t="n">
-        <v>19.5</v>
+        <v>21.3</v>
       </c>
       <c r="G10" t="n">
         <v>241.57</v>
       </c>
       <c r="H10" t="n">
-        <v>3.38</v>
+        <v>5.02</v>
       </c>
       <c r="I10" t="n">
-        <v>58.03</v>
+        <v>60.44</v>
       </c>
       <c r="J10" t="n">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="K10" t="n">
         <v>61.25</v>
@@ -1268,34 +1268,34 @@
         <v>74.34999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>249.74</v>
+        <v>253.7</v>
       </c>
       <c r="O10" t="n">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99896</v>
+        <v>99957.8</v>
       </c>
       <c r="R10" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>224.77</v>
+        <v>228.33</v>
       </c>
       <c r="T10" t="n">
-        <v>9989.6</v>
+        <v>9995.780000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>292.2</v>
+        <v>299.37</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>16982.32</v>
+        <v>17992.4</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>140.6</v>
+        <v>771.2</v>
       </c>
       <c r="E11" t="n">
-        <v>93.98</v>
+        <v>546.61</v>
       </c>
       <c r="F11" t="n">
-        <v>49.61</v>
+        <v>41.09</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>659.2</v>
       </c>
       <c r="H11" t="n">
-        <v>23.33</v>
+        <v>16.99</v>
       </c>
       <c r="I11" t="n">
-        <v>84.72</v>
+        <v>61.45</v>
       </c>
       <c r="J11" t="n">
-        <v>10.69</v>
+        <v>0.87</v>
       </c>
       <c r="K11" t="n">
         <v>61.25</v>
       </c>
       <c r="L11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M11" t="n">
-        <v>73.55</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>140.6</v>
+        <v>771.2</v>
       </c>
       <c r="O11" t="n">
-        <v>711</v>
+        <v>129</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99966.60000000001</v>
+        <v>99484.8</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>126.54</v>
+        <v>694.08</v>
       </c>
       <c r="T11" t="n">
-        <v>9996.66</v>
+        <v>9948.48</v>
       </c>
       <c r="U11" t="n">
-        <v>163.1</v>
+        <v>910.02</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W11" t="n">
-        <v>15994.66</v>
+        <v>17907.26</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -554,72 +554,72 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82.40000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>72.76000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="F2" t="n">
-        <v>13.24</v>
+        <v>18.42</v>
       </c>
       <c r="G2" t="n">
         <v>58.79</v>
       </c>
       <c r="H2" t="n">
-        <v>40.16</v>
+        <v>46.83</v>
       </c>
       <c r="I2" t="n">
-        <v>52.72</v>
+        <v>63.48</v>
       </c>
       <c r="J2" t="n">
-        <v>1.25</v>
+        <v>3.01</v>
       </c>
       <c r="K2" t="n">
-        <v>66.25</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>79.75</v>
+        <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>82.40000000000001</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1213</v>
+        <v>1158</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99951.2</v>
+        <v>99958.56</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>74.16</v>
+        <v>77.69</v>
       </c>
       <c r="T2" t="n">
-        <v>9995.120000000001</v>
+        <v>9995.860000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>94.76000000000001</v>
+        <v>103.58</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>14992.68</v>
+        <v>19991.71</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -634,77 +634,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UFLEX</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>701.8</v>
+        <v>587.35</v>
       </c>
       <c r="E3" t="n">
-        <v>461.11</v>
+        <v>492.72</v>
       </c>
       <c r="F3" t="n">
-        <v>52.2</v>
+        <v>19.21</v>
       </c>
       <c r="G3" t="n">
-        <v>685.6</v>
+        <v>539</v>
       </c>
       <c r="H3" t="n">
-        <v>2.36</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>80.79000000000001</v>
+        <v>61.55</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="K3" t="n">
-        <v>61.25</v>
+        <v>72.5</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>76.75</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>701.8</v>
+        <v>587.35</v>
       </c>
       <c r="O3" t="n">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99655.60000000001</v>
+        <v>99849.5</v>
       </c>
       <c r="R3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S3" t="n">
-        <v>631.62</v>
+        <v>528.62</v>
       </c>
       <c r="T3" t="n">
-        <v>9965.559999999999</v>
+        <v>9984.950000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>814.09</v>
+        <v>704.8200000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="W3" t="n">
-        <v>15944.9</v>
+        <v>19969.9</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MODERATE CONVICTION</t>
+          <t>HIGH CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CORDSCABLE</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>315.5</v>
+        <v>339.75</v>
       </c>
       <c r="E4" t="n">
-        <v>192.52</v>
+        <v>243.02</v>
       </c>
       <c r="F4" t="n">
-        <v>63.88</v>
+        <v>39.8</v>
       </c>
       <c r="G4" t="n">
-        <v>216.6</v>
+        <v>220.4</v>
       </c>
       <c r="H4" t="n">
-        <v>45.66</v>
+        <v>54.15</v>
       </c>
       <c r="I4" t="n">
-        <v>83.53</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.28</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>61.25</v>
+        <v>66.25</v>
       </c>
       <c r="L4" t="n">
         <v>100</v>
       </c>
       <c r="M4" t="n">
-        <v>76.75</v>
+        <v>79.75</v>
       </c>
       <c r="N4" t="n">
-        <v>315.5</v>
+        <v>339.75</v>
       </c>
       <c r="O4" t="n">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99698</v>
+        <v>99886.5</v>
       </c>
       <c r="R4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="S4" t="n">
-        <v>283.95</v>
+        <v>305.78</v>
       </c>
       <c r="T4" t="n">
-        <v>9969.799999999999</v>
+        <v>9988.65</v>
       </c>
       <c r="U4" t="n">
-        <v>365.98</v>
+        <v>400.9</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
-        <v>15951.68</v>
+        <v>17979.57</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>520.65</v>
+        <v>777.4</v>
       </c>
       <c r="E5" t="n">
-        <v>209.44</v>
+        <v>547.6</v>
       </c>
       <c r="F5" t="n">
-        <v>148.6</v>
+        <v>41.97</v>
       </c>
       <c r="G5" t="n">
-        <v>197.45</v>
+        <v>659.2</v>
       </c>
       <c r="H5" t="n">
-        <v>163.69</v>
+        <v>17.93</v>
       </c>
       <c r="I5" t="n">
-        <v>86.31999999999999</v>
+        <v>62.48</v>
       </c>
       <c r="J5" t="n">
-        <v>3.61</v>
+        <v>1.21</v>
       </c>
       <c r="K5" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>76.75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>520.65</v>
+        <v>777.4</v>
       </c>
       <c r="O5" t="n">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99964.8</v>
+        <v>99507.2</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>468.58</v>
+        <v>699.66</v>
       </c>
       <c r="T5" t="n">
-        <v>9996.48</v>
+        <v>9950.719999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>603.95</v>
+        <v>925.11</v>
       </c>
       <c r="V5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W5" t="n">
-        <v>15994.37</v>
+        <v>18906.37</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BEPL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>330.35</v>
+        <v>129.74</v>
       </c>
       <c r="E6" t="n">
-        <v>242.2</v>
+        <v>96.66</v>
       </c>
       <c r="F6" t="n">
-        <v>36.4</v>
+        <v>34.22</v>
       </c>
       <c r="G6" t="n">
-        <v>220.4</v>
+        <v>108.59</v>
       </c>
       <c r="H6" t="n">
-        <v>49.89</v>
+        <v>19.48</v>
       </c>
       <c r="I6" t="n">
-        <v>62.1</v>
+        <v>60.59</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M6" t="n">
-        <v>76.75</v>
+        <v>78.8</v>
       </c>
       <c r="N6" t="n">
-        <v>330.35</v>
+        <v>129.74</v>
       </c>
       <c r="O6" t="n">
-        <v>302</v>
+        <v>770</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99765.7</v>
+        <v>99899.8</v>
       </c>
       <c r="R6" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="S6" t="n">
-        <v>297.32</v>
+        <v>116.77</v>
       </c>
       <c r="T6" t="n">
-        <v>9976.57</v>
+        <v>9989.98</v>
       </c>
       <c r="U6" t="n">
-        <v>389.81</v>
+        <v>154.39</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>17957.83</v>
+        <v>18980.96</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>602.35</v>
+        <v>942.45</v>
       </c>
       <c r="E7" t="n">
-        <v>475.47</v>
+        <v>680.58</v>
       </c>
       <c r="F7" t="n">
-        <v>26.69</v>
+        <v>38.48</v>
       </c>
       <c r="G7" t="n">
-        <v>520.6</v>
+        <v>513.55</v>
       </c>
       <c r="H7" t="n">
-        <v>15.7</v>
+        <v>83.52</v>
       </c>
       <c r="I7" t="n">
-        <v>63.55</v>
+        <v>67.38</v>
       </c>
       <c r="J7" t="n">
-        <v>18.27</v>
+        <v>1.67</v>
       </c>
       <c r="K7" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="L7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>75.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>602.35</v>
+        <v>942.45</v>
       </c>
       <c r="O7" t="n">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99990.10000000001</v>
+        <v>99899.7</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="S7" t="n">
-        <v>542.12</v>
+        <v>848.2</v>
       </c>
       <c r="T7" t="n">
-        <v>9999.01</v>
+        <v>9989.969999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>716.8</v>
+        <v>1140.36</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W7" t="n">
-        <v>18998.12</v>
+        <v>20978.94</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>GOCLCORP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>133.73</v>
+        <v>422.95</v>
       </c>
       <c r="E8" t="n">
-        <v>95.86</v>
+        <v>328.1</v>
       </c>
       <c r="F8" t="n">
-        <v>39.51</v>
+        <v>28.91</v>
       </c>
       <c r="G8" t="n">
-        <v>129.89</v>
+        <v>401.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>5.29</v>
       </c>
       <c r="I8" t="n">
-        <v>80.31999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.79</v>
+        <v>13.38</v>
       </c>
       <c r="K8" t="n">
-        <v>58.75</v>
+        <v>75</v>
       </c>
       <c r="L8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M8" t="n">
-        <v>75.25</v>
+        <v>77</v>
       </c>
       <c r="N8" t="n">
-        <v>133.73</v>
+        <v>422.95</v>
       </c>
       <c r="O8" t="n">
-        <v>747</v>
+        <v>236</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99896.31</v>
+        <v>99816.2</v>
       </c>
       <c r="R8" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S8" t="n">
-        <v>120.36</v>
+        <v>380.66</v>
       </c>
       <c r="T8" t="n">
-        <v>9989.629999999999</v>
+        <v>9981.620000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>155.13</v>
+        <v>511.77</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W8" t="n">
-        <v>15983.41</v>
+        <v>20961.4</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12158</v>
+        <v>344.6</v>
       </c>
       <c r="E9" t="n">
-        <v>8942.139999999999</v>
+        <v>297.08</v>
       </c>
       <c r="F9" t="n">
-        <v>35.96</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>9950</v>
+        <v>220</v>
       </c>
       <c r="H9" t="n">
-        <v>22.19</v>
+        <v>56.64</v>
       </c>
       <c r="I9" t="n">
-        <v>59.12</v>
+        <v>45.19</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="K9" t="n">
-        <v>66.25</v>
+        <v>61.25</v>
       </c>
       <c r="L9" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>74.55</v>
+        <v>76.75</v>
       </c>
       <c r="N9" t="n">
-        <v>12158</v>
+        <v>344.6</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>97264</v>
+        <v>99934</v>
       </c>
       <c r="R9" t="n">
-        <v>9.73</v>
+        <v>9.99</v>
       </c>
       <c r="S9" t="n">
-        <v>10942.2</v>
+        <v>310.14</v>
       </c>
       <c r="T9" t="n">
-        <v>9726.4</v>
+        <v>9993.4</v>
       </c>
       <c r="U9" t="n">
-        <v>14346.44</v>
+        <v>396.29</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>17507.52</v>
+        <v>14990.1</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SREEL</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>253.7</v>
+        <v>1013.3</v>
       </c>
       <c r="E10" t="n">
-        <v>209.14</v>
+        <v>642.63</v>
       </c>
       <c r="F10" t="n">
-        <v>21.3</v>
+        <v>57.68</v>
       </c>
       <c r="G10" t="n">
-        <v>241.57</v>
+        <v>720</v>
       </c>
       <c r="H10" t="n">
-        <v>5.02</v>
+        <v>40.74</v>
       </c>
       <c r="I10" t="n">
-        <v>60.44</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.75</v>
+        <v>11.36</v>
       </c>
       <c r="K10" t="n">
-        <v>61.25</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M10" t="n">
-        <v>74.34999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>253.7</v>
+        <v>1013.3</v>
       </c>
       <c r="O10" t="n">
-        <v>394</v>
+        <v>98</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99957.8</v>
+        <v>99303.39999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="S10" t="n">
-        <v>228.33</v>
+        <v>911.97</v>
       </c>
       <c r="T10" t="n">
-        <v>9995.780000000001</v>
+        <v>9930.34</v>
       </c>
       <c r="U10" t="n">
-        <v>299.37</v>
+        <v>1195.69</v>
       </c>
       <c r="V10" t="n">
         <v>18</v>
       </c>
       <c r="W10" t="n">
-        <v>17992.4</v>
+        <v>17874.61</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>CENTENKA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>771.2</v>
+        <v>616.65</v>
       </c>
       <c r="E11" t="n">
-        <v>546.61</v>
+        <v>476.27</v>
       </c>
       <c r="F11" t="n">
-        <v>41.09</v>
+        <v>29.47</v>
       </c>
       <c r="G11" t="n">
-        <v>659.2</v>
+        <v>520.6</v>
       </c>
       <c r="H11" t="n">
-        <v>16.99</v>
+        <v>18.45</v>
       </c>
       <c r="I11" t="n">
-        <v>61.45</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.87</v>
+        <v>3.03</v>
       </c>
       <c r="K11" t="n">
-        <v>61.25</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>74.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>771.2</v>
+        <v>616.65</v>
       </c>
       <c r="O11" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99484.8</v>
+        <v>99897.3</v>
       </c>
       <c r="R11" t="n">
-        <v>9.949999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="S11" t="n">
-        <v>694.08</v>
+        <v>554.98</v>
       </c>
       <c r="T11" t="n">
-        <v>9948.48</v>
+        <v>9989.73</v>
       </c>
       <c r="U11" t="n">
-        <v>910.02</v>
+        <v>733.8099999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W11" t="n">
-        <v>17907.26</v>
+        <v>18980.49</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>

--- a/output/NSE_Portfolio_Recommendations.xlsx
+++ b/output/NSE_Portfolio_Recommendations.xlsx
@@ -549,77 +549,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>86.31999999999999</v>
+        <v>814.1</v>
       </c>
       <c r="E2" t="n">
-        <v>72.89</v>
+        <v>548.8</v>
       </c>
       <c r="F2" t="n">
-        <v>18.42</v>
+        <v>48.34</v>
       </c>
       <c r="G2" t="n">
-        <v>58.79</v>
+        <v>659.2</v>
       </c>
       <c r="H2" t="n">
-        <v>46.83</v>
+        <v>23.5</v>
       </c>
       <c r="I2" t="n">
-        <v>63.48</v>
+        <v>67.94</v>
       </c>
       <c r="J2" t="n">
-        <v>3.01</v>
+        <v>1.35</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>85</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>86.31999999999999</v>
+        <v>814.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1158</v>
+        <v>122</v>
       </c>
       <c r="P2" t="n">
         <v>100000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99958.56</v>
+        <v>99320.2</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="S2" t="n">
-        <v>77.69</v>
+        <v>732.6900000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>9995.860000000001</v>
+        <v>9932.02</v>
       </c>
       <c r="U2" t="n">
-        <v>103.58</v>
+        <v>968.78</v>
       </c>
       <c r="V2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W2" t="n">
-        <v>19991.71</v>
+        <v>18870.84</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -639,72 +639,72 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="E3" t="n">
-        <v>492.72</v>
+        <v>493.23</v>
       </c>
       <c r="F3" t="n">
-        <v>19.21</v>
+        <v>20.98</v>
       </c>
       <c r="G3" t="n">
         <v>539</v>
       </c>
       <c r="H3" t="n">
-        <v>8.970000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="I3" t="n">
-        <v>61.55</v>
+        <v>65.02</v>
       </c>
       <c r="J3" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="K3" t="n">
-        <v>72.5</v>
+        <v>70</v>
       </c>
       <c r="L3" t="n">
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>81.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>587.35</v>
+        <v>596.7</v>
       </c>
       <c r="O3" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P3" t="n">
         <v>100000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99849.5</v>
+        <v>99648.89999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>528.62</v>
+        <v>537.03</v>
       </c>
       <c r="T3" t="n">
-        <v>9984.950000000001</v>
+        <v>9964.889999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>704.8200000000001</v>
+        <v>710.0700000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
-        <v>19969.9</v>
+        <v>18933.29</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HIGH CONVICTION</t>
+          <t>MODERATE CONVICTION</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -719,73 +719,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>339.75</v>
+        <v>957.15</v>
       </c>
       <c r="E4" t="n">
-        <v>243.02</v>
+        <v>644.87</v>
       </c>
       <c r="F4" t="n">
-        <v>39.8</v>
+        <v>48.43</v>
       </c>
       <c r="G4" t="n">
-        <v>220.4</v>
+        <v>720</v>
       </c>
       <c r="H4" t="n">
-        <v>54.15</v>
+        <v>32.94</v>
       </c>
       <c r="I4" t="n">
-        <v>66.98999999999999</v>
+        <v>64.95</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>2.51</v>
       </c>
       <c r="K4" t="n">
-        <v>66.25</v>
+        <v>75</v>
       </c>
       <c r="L4" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="M4" t="n">
-        <v>79.75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>339.75</v>
+        <v>957.15</v>
       </c>
       <c r="O4" t="n">
-        <v>294</v>
+        <v>104</v>
       </c>
       <c r="P4" t="n">
         <v>100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>99886.5</v>
+        <v>99543.60000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>9.99</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>305.78</v>
+        <v>861.4400000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>9988.65</v>
+        <v>9954.360000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>400.9</v>
+        <v>1158.15</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>17979.57</v>
+        <v>20904.16</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -804,73 +804,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>DICIND</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>777.4</v>
+        <v>618.6</v>
       </c>
       <c r="E5" t="n">
-        <v>547.6</v>
+        <v>520.8099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>41.97</v>
+        <v>18.78</v>
       </c>
       <c r="G5" t="n">
-        <v>659.2</v>
+        <v>570</v>
       </c>
       <c r="H5" t="n">
-        <v>17.93</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>62.48</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>79.59999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="N5" t="n">
-        <v>777.4</v>
+        <v>618.6</v>
       </c>
       <c r="O5" t="n">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="P5" t="n">
         <v>100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>99507.2</v>
+        <v>99594.60000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.949999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>699.66</v>
+        <v>556.74</v>
       </c>
       <c r="T5" t="n">
-        <v>9950.719999999999</v>
+        <v>9959.459999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>925.11</v>
+        <v>742.3200000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W5" t="n">
-        <v>18906.37</v>
+        <v>19918.92</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -889,73 +889,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BEPL</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>129.74</v>
+        <v>11.86</v>
       </c>
       <c r="E6" t="n">
-        <v>96.66</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>34.22</v>
+        <v>23.41</v>
       </c>
       <c r="G6" t="n">
-        <v>108.59</v>
+        <v>11.38</v>
       </c>
       <c r="H6" t="n">
-        <v>19.48</v>
+        <v>4.22</v>
       </c>
       <c r="I6" t="n">
-        <v>60.59</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.37</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="M6" t="n">
-        <v>78.8</v>
+        <v>77</v>
       </c>
       <c r="N6" t="n">
-        <v>129.74</v>
+        <v>11.86</v>
       </c>
       <c r="O6" t="n">
-        <v>770</v>
+        <v>8431</v>
       </c>
       <c r="P6" t="n">
         <v>100000</v>
       </c>
       <c r="Q6" t="n">
-        <v>99899.8</v>
+        <v>99991.66</v>
       </c>
       <c r="R6" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>116.77</v>
+        <v>10.67</v>
       </c>
       <c r="T6" t="n">
-        <v>9989.98</v>
+        <v>9999.17</v>
       </c>
       <c r="U6" t="n">
-        <v>154.39</v>
+        <v>14.35</v>
       </c>
       <c r="V6" t="n">
-        <v>19</v>
+        <v>20.99</v>
       </c>
       <c r="W6" t="n">
-        <v>18980.96</v>
+        <v>20988.25</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -974,73 +974,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>942.45</v>
+        <v>340.1</v>
       </c>
       <c r="E7" t="n">
-        <v>680.58</v>
+        <v>243.84</v>
       </c>
       <c r="F7" t="n">
-        <v>38.48</v>
+        <v>39.48</v>
       </c>
       <c r="G7" t="n">
-        <v>513.55</v>
+        <v>220.4</v>
       </c>
       <c r="H7" t="n">
-        <v>83.52</v>
+        <v>54.31</v>
       </c>
       <c r="I7" t="n">
-        <v>67.38</v>
+        <v>67.16</v>
       </c>
       <c r="J7" t="n">
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="K7" t="n">
-        <v>72.5</v>
+        <v>61.25</v>
       </c>
       <c r="L7" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>77.09999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="N7" t="n">
-        <v>942.45</v>
+        <v>340.1</v>
       </c>
       <c r="O7" t="n">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="P7" t="n">
         <v>100000</v>
       </c>
       <c r="Q7" t="n">
-        <v>99899.7</v>
+        <v>99989.39999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>848.2</v>
+        <v>306.09</v>
       </c>
       <c r="T7" t="n">
-        <v>9989.969999999999</v>
+        <v>9998.940000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>1140.36</v>
+        <v>401.32</v>
       </c>
       <c r="V7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>20978.94</v>
+        <v>17998.09</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1059,73 +1059,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GOCLCORP</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>422.95</v>
+        <v>85.95</v>
       </c>
       <c r="E8" t="n">
-        <v>328.1</v>
+        <v>73.02</v>
       </c>
       <c r="F8" t="n">
-        <v>28.91</v>
+        <v>17.71</v>
       </c>
       <c r="G8" t="n">
-        <v>401.7</v>
+        <v>58.79</v>
       </c>
       <c r="H8" t="n">
-        <v>5.29</v>
+        <v>46.2</v>
       </c>
       <c r="I8" t="n">
-        <v>60.8</v>
+        <v>62.05</v>
       </c>
       <c r="J8" t="n">
-        <v>13.38</v>
+        <v>0.84</v>
       </c>
       <c r="K8" t="n">
-        <v>75</v>
+        <v>61.25</v>
       </c>
       <c r="L8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>77</v>
+        <v>76.75</v>
       </c>
       <c r="N8" t="n">
-        <v>422.95</v>
+        <v>85.95</v>
       </c>
       <c r="O8" t="n">
-        <v>236</v>
+        <v>1163</v>
       </c>
       <c r="P8" t="n">
         <v>100000</v>
       </c>
       <c r="Q8" t="n">
-        <v>99816.2</v>
+        <v>99959.85000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>380.66</v>
+        <v>77.36</v>
       </c>
       <c r="T8" t="n">
-        <v>9981.620000000001</v>
+        <v>9995.98</v>
       </c>
       <c r="U8" t="n">
-        <v>511.77</v>
+        <v>100.56</v>
       </c>
       <c r="V8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>20961.4</v>
+        <v>16993.17</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1144,73 +1144,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>344.6</v>
+        <v>62.81</v>
       </c>
       <c r="E9" t="n">
-        <v>297.08</v>
+        <v>49.72</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>26.32</v>
       </c>
       <c r="G9" t="n">
-        <v>220</v>
+        <v>62.84</v>
       </c>
       <c r="H9" t="n">
-        <v>56.64</v>
+        <v>-0.05</v>
       </c>
       <c r="I9" t="n">
-        <v>45.19</v>
+        <v>75.44</v>
       </c>
       <c r="J9" t="n">
-        <v>1.38</v>
+        <v>3.16</v>
       </c>
       <c r="K9" t="n">
-        <v>61.25</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>76.75</v>
+        <v>76</v>
       </c>
       <c r="N9" t="n">
-        <v>344.6</v>
+        <v>62.81</v>
       </c>
       <c r="O9" t="n">
-        <v>290</v>
+        <v>1592</v>
       </c>
       <c r="P9" t="n">
         <v>100000</v>
       </c>
       <c r="Q9" t="n">
-        <v>99934</v>
+        <v>99993.52</v>
       </c>
       <c r="R9" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>310.14</v>
+        <v>56.53</v>
       </c>
       <c r="T9" t="n">
-        <v>9993.4</v>
+        <v>9999.35</v>
       </c>
       <c r="U9" t="n">
-        <v>396.29</v>
+        <v>72.86</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W9" t="n">
-        <v>14990.1</v>
+        <v>15998.96</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1229,73 +1229,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ANTELOPUS</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1013.3</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>642.63</v>
+        <v>86.5</v>
       </c>
       <c r="F10" t="n">
-        <v>57.68</v>
+        <v>2.94</v>
       </c>
       <c r="G10" t="n">
-        <v>720</v>
+        <v>53</v>
       </c>
       <c r="H10" t="n">
-        <v>40.74</v>
+        <v>68</v>
       </c>
       <c r="I10" t="n">
-        <v>74.90000000000001</v>
+        <v>40.78</v>
       </c>
       <c r="J10" t="n">
-        <v>11.36</v>
+        <v>7.28</v>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>81.25</v>
       </c>
       <c r="L10" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>75.59999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="N10" t="n">
-        <v>1013.3</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>98</v>
+        <v>1123</v>
       </c>
       <c r="P10" t="n">
         <v>100000</v>
       </c>
       <c r="Q10" t="n">
-        <v>99303.39999999999</v>
+        <v>99991.92</v>
       </c>
       <c r="R10" t="n">
-        <v>9.93</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>911.97</v>
+        <v>80.14</v>
       </c>
       <c r="T10" t="n">
-        <v>9930.34</v>
+        <v>9999.190000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1195.69</v>
+        <v>107.74</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W10" t="n">
-        <v>17874.61</v>
+        <v>20998.3</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NOT A RECOVERY</t>
+          <t>STRONG RETEST</t>
         </is>
       </c>
     </row>
@@ -1314,73 +1314,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CENTENKA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>616.65</v>
+        <v>236.01</v>
       </c>
       <c r="E11" t="n">
-        <v>476.27</v>
+        <v>205.62</v>
       </c>
       <c r="F11" t="n">
-        <v>29.47</v>
+        <v>14.78</v>
       </c>
       <c r="G11" t="n">
-        <v>520.6</v>
+        <v>245.38</v>
       </c>
       <c r="H11" t="n">
-        <v>18.45</v>
+        <v>-3.82</v>
       </c>
       <c r="I11" t="n">
-        <v>67.23999999999999</v>
+        <v>61.53</v>
       </c>
       <c r="J11" t="n">
-        <v>3.03</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>75</v>
+        <v>58.75</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>75.40000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="N11" t="n">
-        <v>616.65</v>
+        <v>236.01</v>
       </c>
       <c r="O11" t="n">
-        <v>162</v>
+        <v>423</v>
       </c>
       <c r="P11" t="n">
         <v>100000</v>
       </c>
       <c r="Q11" t="n">
-        <v>99897.3</v>
+        <v>99832.23</v>
       </c>
       <c r="R11" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="S11" t="n">
-        <v>554.98</v>
+        <v>212.41</v>
       </c>
       <c r="T11" t="n">
-        <v>9989.73</v>
+        <v>9983.219999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>733.8099999999999</v>
+        <v>276.13</v>
       </c>
       <c r="V11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>18980.49</v>
+        <v>16971.48</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
